--- a/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao_20.xlsx
+++ b/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao_20.xlsx
@@ -76,7 +76,7 @@
     <t>Rodada 19</t>
   </si>
   <si>
-    <t>Parcial Rodada 1</t>
+    <t>Parcial Rodada 2</t>
   </si>
   <si>
     <t>time_id</t>
@@ -576,10 +576,10 @@
         <v>22</v>
       </c>
       <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="V2">
-        <v>55.66</v>
+        <v>55.659912109375</v>
+      </c>
+      <c r="D2">
+        <v>55.659912109375</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -590,10 +590,10 @@
         <v>23</v>
       </c>
       <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="V3">
-        <v>54.9</v>
+        <v>54.89990234375</v>
+      </c>
+      <c r="D3">
+        <v>54.89990234375</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -604,10 +604,10 @@
         <v>24</v>
       </c>
       <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="V4">
-        <v>53.66</v>
+        <v>53.659912109375</v>
+      </c>
+      <c r="D4">
+        <v>53.659912109375</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -618,10 +618,10 @@
         <v>25</v>
       </c>
       <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="V5">
-        <v>66.37</v>
+        <v>66.3701171875</v>
+      </c>
+      <c r="D5">
+        <v>66.3701171875</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -632,10 +632,10 @@
         <v>26</v>
       </c>
       <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="V6">
-        <v>68.06</v>
+        <v>68.06005859375</v>
+      </c>
+      <c r="D6">
+        <v>68.06005859375</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -646,10 +646,10 @@
         <v>27</v>
       </c>
       <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="V7">
-        <v>60.6</v>
+        <v>60.60009765625</v>
+      </c>
+      <c r="D7">
+        <v>60.60009765625</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -660,10 +660,10 @@
         <v>28</v>
       </c>
       <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="V8">
-        <v>47.86</v>
+        <v>47.860107421875</v>
+      </c>
+      <c r="D8">
+        <v>47.860107421875</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -674,10 +674,10 @@
         <v>29</v>
       </c>
       <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="V9">
-        <v>47.86</v>
+        <v>47.860107421875</v>
+      </c>
+      <c r="D9">
+        <v>47.860107421875</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -688,10 +688,10 @@
         <v>30</v>
       </c>
       <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="V10">
-        <v>55.66</v>
+        <v>55.659912109375</v>
+      </c>
+      <c r="D10">
+        <v>55.659912109375</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -702,10 +702,10 @@
         <v>31</v>
       </c>
       <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="V11">
-        <v>71.95999999999999</v>
+        <v>71.9599609375</v>
+      </c>
+      <c r="D11">
+        <v>71.9599609375</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -716,10 +716,10 @@
         <v>32</v>
       </c>
       <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="V12">
-        <v>83.2</v>
+        <v>83.2001953125</v>
+      </c>
+      <c r="D12">
+        <v>83.2001953125</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -732,9 +732,6 @@
       <c r="C13">
         <v>0</v>
       </c>
-      <c r="V13">
-        <v>0</v>
-      </c>
     </row>
     <row r="14" spans="1:22">
       <c r="A14" s="1">
@@ -744,10 +741,10 @@
         <v>34</v>
       </c>
       <c r="C14">
-        <v>0</v>
-      </c>
-      <c r="V14">
-        <v>67.16</v>
+        <v>67.16015625</v>
+      </c>
+      <c r="D14">
+        <v>67.16015625</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -758,10 +755,10 @@
         <v>35</v>
       </c>
       <c r="C15">
-        <v>0</v>
-      </c>
-      <c r="V15">
-        <v>61.56</v>
+        <v>61.56005859375</v>
+      </c>
+      <c r="D15">
+        <v>61.56005859375</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -772,13 +769,13 @@
         <v>36</v>
       </c>
       <c r="C16">
-        <v>0</v>
-      </c>
-      <c r="V16">
-        <v>56.05</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22">
+        <v>56.050048828125</v>
+      </c>
+      <c r="D16">
+        <v>56.050048828125</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
       <c r="A17" s="1">
         <v>19209079</v>
       </c>
@@ -786,13 +783,13 @@
         <v>37</v>
       </c>
       <c r="C17">
-        <v>0</v>
-      </c>
-      <c r="V17">
-        <v>63.56</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22">
+        <v>63.56005859375</v>
+      </c>
+      <c r="D17">
+        <v>63.56005859375</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
       <c r="A18" s="1">
         <v>19833277</v>
       </c>
@@ -800,13 +797,13 @@
         <v>38</v>
       </c>
       <c r="C18">
-        <v>0</v>
-      </c>
-      <c r="V18">
         <v>64.5</v>
       </c>
-    </row>
-    <row r="19" spans="1:22">
+      <c r="D18">
+        <v>64.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
       <c r="A19" s="1">
         <v>20651178</v>
       </c>
@@ -814,13 +811,13 @@
         <v>39</v>
       </c>
       <c r="C19">
-        <v>0</v>
-      </c>
-      <c r="V19">
-        <v>61.16</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22">
+        <v>61.159912109375</v>
+      </c>
+      <c r="D19">
+        <v>61.159912109375</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
       <c r="A20" s="1">
         <v>44810918</v>
       </c>
@@ -828,13 +825,13 @@
         <v>40</v>
       </c>
       <c r="C20">
-        <v>0</v>
-      </c>
-      <c r="V20">
-        <v>62.56</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22">
+        <v>62.56005859375</v>
+      </c>
+      <c r="D20">
+        <v>62.56005859375</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
       <c r="A21" s="1">
         <v>47775950</v>
       </c>
@@ -842,10 +839,10 @@
         <v>41</v>
       </c>
       <c r="C21">
-        <v>0</v>
-      </c>
-      <c r="V21">
-        <v>54.05</v>
+        <v>54.050048828125</v>
+      </c>
+      <c r="D21">
+        <v>54.050048828125</v>
       </c>
     </row>
   </sheetData>

--- a/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao_20.xlsx
+++ b/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao_20.xlsx
@@ -581,6 +581,9 @@
       <c r="D2">
         <v>55.659912109375</v>
       </c>
+      <c r="V2">
+        <v>38.9</v>
+      </c>
     </row>
     <row r="3" spans="1:22">
       <c r="A3" s="1">
@@ -595,6 +598,9 @@
       <c r="D3">
         <v>54.89990234375</v>
       </c>
+      <c r="V3">
+        <v>47.35</v>
+      </c>
     </row>
     <row r="4" spans="1:22">
       <c r="A4" s="1">
@@ -609,6 +615,9 @@
       <c r="D4">
         <v>53.659912109375</v>
       </c>
+      <c r="V4">
+        <v>49.8</v>
+      </c>
     </row>
     <row r="5" spans="1:22">
       <c r="A5" s="1">
@@ -623,6 +632,9 @@
       <c r="D5">
         <v>66.3701171875</v>
       </c>
+      <c r="V5">
+        <v>28.7</v>
+      </c>
     </row>
     <row r="6" spans="1:22">
       <c r="A6" s="1">
@@ -637,6 +649,9 @@
       <c r="D6">
         <v>68.06005859375</v>
       </c>
+      <c r="V6">
+        <v>41.7</v>
+      </c>
     </row>
     <row r="7" spans="1:22">
       <c r="A7" s="1">
@@ -651,6 +666,9 @@
       <c r="D7">
         <v>60.60009765625</v>
       </c>
+      <c r="V7">
+        <v>48.95</v>
+      </c>
     </row>
     <row r="8" spans="1:22">
       <c r="A8" s="1">
@@ -665,6 +683,9 @@
       <c r="D8">
         <v>47.860107421875</v>
       </c>
+      <c r="V8">
+        <v>67.25</v>
+      </c>
     </row>
     <row r="9" spans="1:22">
       <c r="A9" s="1">
@@ -679,6 +700,9 @@
       <c r="D9">
         <v>47.860107421875</v>
       </c>
+      <c r="V9">
+        <v>52.8</v>
+      </c>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" s="1">
@@ -693,6 +717,9 @@
       <c r="D10">
         <v>55.659912109375</v>
       </c>
+      <c r="V10">
+        <v>18.8</v>
+      </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="1">
@@ -707,6 +734,9 @@
       <c r="D11">
         <v>71.9599609375</v>
       </c>
+      <c r="V11">
+        <v>53.6</v>
+      </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1">
@@ -721,6 +751,9 @@
       <c r="D12">
         <v>83.2001953125</v>
       </c>
+      <c r="V12">
+        <v>83.5</v>
+      </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="1">
@@ -732,6 +765,9 @@
       <c r="C13">
         <v>0</v>
       </c>
+      <c r="V13">
+        <v>63.85</v>
+      </c>
     </row>
     <row r="14" spans="1:22">
       <c r="A14" s="1">
@@ -746,6 +782,9 @@
       <c r="D14">
         <v>67.16015625</v>
       </c>
+      <c r="V14">
+        <v>62.35</v>
+      </c>
     </row>
     <row r="15" spans="1:22">
       <c r="A15" s="1">
@@ -760,6 +799,9 @@
       <c r="D15">
         <v>61.56005859375</v>
       </c>
+      <c r="V15">
+        <v>41.7</v>
+      </c>
     </row>
     <row r="16" spans="1:22">
       <c r="A16" s="1">
@@ -774,8 +816,11 @@
       <c r="D16">
         <v>56.050048828125</v>
       </c>
-    </row>
-    <row r="17" spans="1:4">
+      <c r="V16">
+        <v>57.25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22">
       <c r="A17" s="1">
         <v>19209079</v>
       </c>
@@ -788,8 +833,11 @@
       <c r="D17">
         <v>63.56005859375</v>
       </c>
-    </row>
-    <row r="18" spans="1:4">
+      <c r="V17">
+        <v>82.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22">
       <c r="A18" s="1">
         <v>19833277</v>
       </c>
@@ -802,8 +850,11 @@
       <c r="D18">
         <v>64.5</v>
       </c>
-    </row>
-    <row r="19" spans="1:4">
+      <c r="V18">
+        <v>42.8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22">
       <c r="A19" s="1">
         <v>20651178</v>
       </c>
@@ -816,8 +867,11 @@
       <c r="D19">
         <v>61.159912109375</v>
       </c>
-    </row>
-    <row r="20" spans="1:4">
+      <c r="V19">
+        <v>57.65</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22">
       <c r="A20" s="1">
         <v>44810918</v>
       </c>
@@ -830,8 +884,11 @@
       <c r="D20">
         <v>62.56005859375</v>
       </c>
-    </row>
-    <row r="21" spans="1:4">
+      <c r="V20">
+        <v>55.9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22">
       <c r="A21" s="1">
         <v>47775950</v>
       </c>
@@ -843,6 +900,9 @@
       </c>
       <c r="D21">
         <v>54.050048828125</v>
+      </c>
+      <c r="V21">
+        <v>51.15</v>
       </c>
     </row>
   </sheetData>

--- a/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao_20.xlsx
+++ b/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao_20.xlsx
@@ -701,7 +701,7 @@
         <v>47.860107421875</v>
       </c>
       <c r="V9">
-        <v>52.8</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="10" spans="1:22">

--- a/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao_20.xlsx
+++ b/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao_20.xlsx
@@ -582,7 +582,7 @@
         <v>55.659912109375</v>
       </c>
       <c r="V2">
-        <v>38.9</v>
+        <v>59.6</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -599,7 +599,7 @@
         <v>54.89990234375</v>
       </c>
       <c r="V3">
-        <v>47.35</v>
+        <v>51.65</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -616,7 +616,7 @@
         <v>53.659912109375</v>
       </c>
       <c r="V4">
-        <v>49.8</v>
+        <v>61.41</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -633,7 +633,7 @@
         <v>66.3701171875</v>
       </c>
       <c r="V5">
-        <v>28.7</v>
+        <v>34.41</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -650,7 +650,7 @@
         <v>68.06005859375</v>
       </c>
       <c r="V6">
-        <v>41.7</v>
+        <v>59.81</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -667,7 +667,7 @@
         <v>60.60009765625</v>
       </c>
       <c r="V7">
-        <v>48.95</v>
+        <v>74.16</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -684,7 +684,7 @@
         <v>47.860107421875</v>
       </c>
       <c r="V8">
-        <v>67.25</v>
+        <v>71.55</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -701,7 +701,7 @@
         <v>47.860107421875</v>
       </c>
       <c r="V9">
-        <v>56.2</v>
+        <v>61.91</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -718,7 +718,7 @@
         <v>55.659912109375</v>
       </c>
       <c r="V10">
-        <v>18.8</v>
+        <v>29.81</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -735,7 +735,7 @@
         <v>71.9599609375</v>
       </c>
       <c r="V11">
-        <v>53.6</v>
+        <v>58.41</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -752,7 +752,7 @@
         <v>83.2001953125</v>
       </c>
       <c r="V12">
-        <v>83.5</v>
+        <v>86.90000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -766,7 +766,7 @@
         <v>0</v>
       </c>
       <c r="V13">
-        <v>63.85</v>
+        <v>94.47</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -783,7 +783,7 @@
         <v>67.16015625</v>
       </c>
       <c r="V14">
-        <v>62.35</v>
+        <v>82.55</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -800,7 +800,7 @@
         <v>61.56005859375</v>
       </c>
       <c r="V15">
-        <v>41.7</v>
+        <v>50.81</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -817,7 +817,7 @@
         <v>56.050048828125</v>
       </c>
       <c r="V16">
-        <v>57.25</v>
+        <v>66.25</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -834,7 +834,7 @@
         <v>63.56005859375</v>
       </c>
       <c r="V17">
-        <v>82.5</v>
+        <v>85.90000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -851,7 +851,7 @@
         <v>64.5</v>
       </c>
       <c r="V18">
-        <v>42.8</v>
+        <v>61.71</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -868,7 +868,7 @@
         <v>61.159912109375</v>
       </c>
       <c r="V19">
-        <v>57.65</v>
+        <v>63.36</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -885,7 +885,7 @@
         <v>62.56005859375</v>
       </c>
       <c r="V20">
-        <v>55.9</v>
+        <v>74.01000000000001</v>
       </c>
     </row>
     <row r="21" spans="1:22">
@@ -902,7 +902,7 @@
         <v>54.050048828125</v>
       </c>
       <c r="V21">
-        <v>51.15</v>
+        <v>68.84999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao_20.xlsx
+++ b/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao_20.xlsx
@@ -582,7 +582,7 @@
         <v>55.659912109375</v>
       </c>
       <c r="V2">
-        <v>59.6</v>
+        <v>73.59999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -599,7 +599,7 @@
         <v>54.89990234375</v>
       </c>
       <c r="V3">
-        <v>51.65</v>
+        <v>77.59999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -616,7 +616,7 @@
         <v>53.659912109375</v>
       </c>
       <c r="V4">
-        <v>61.41</v>
+        <v>81.48</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -633,7 +633,7 @@
         <v>66.3701171875</v>
       </c>
       <c r="V5">
-        <v>34.41</v>
+        <v>44.68</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -650,7 +650,7 @@
         <v>68.06005859375</v>
       </c>
       <c r="V6">
-        <v>59.81</v>
+        <v>82.18000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -667,7 +667,7 @@
         <v>60.60009765625</v>
       </c>
       <c r="V7">
-        <v>74.16</v>
+        <v>75.88</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -684,7 +684,7 @@
         <v>47.860107421875</v>
       </c>
       <c r="V8">
-        <v>71.55</v>
+        <v>90.59999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -701,7 +701,7 @@
         <v>47.860107421875</v>
       </c>
       <c r="V9">
-        <v>61.91</v>
+        <v>72.18000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -718,7 +718,7 @@
         <v>55.659912109375</v>
       </c>
       <c r="V10">
-        <v>29.81</v>
+        <v>55.78</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -735,7 +735,7 @@
         <v>71.9599609375</v>
       </c>
       <c r="V11">
-        <v>58.41</v>
+        <v>66.68000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -752,7 +752,7 @@
         <v>83.2001953125</v>
       </c>
       <c r="V12">
-        <v>86.90000000000001</v>
+        <v>98.7</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -766,7 +766,7 @@
         <v>0</v>
       </c>
       <c r="V13">
-        <v>94.47</v>
+        <v>95.41</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -783,7 +783,7 @@
         <v>67.16015625</v>
       </c>
       <c r="V14">
-        <v>82.55</v>
+        <v>86.45</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -800,7 +800,7 @@
         <v>61.56005859375</v>
       </c>
       <c r="V15">
-        <v>50.81</v>
+        <v>83.48</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -817,7 +817,7 @@
         <v>56.050048828125</v>
       </c>
       <c r="V16">
-        <v>66.25</v>
+        <v>70.3</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -834,7 +834,7 @@
         <v>63.56005859375</v>
       </c>
       <c r="V17">
-        <v>85.90000000000001</v>
+        <v>100.5</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -851,7 +851,7 @@
         <v>64.5</v>
       </c>
       <c r="V18">
-        <v>61.71</v>
+        <v>75.68000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -868,7 +868,7 @@
         <v>61.159912109375</v>
       </c>
       <c r="V19">
-        <v>63.36</v>
+        <v>71.18000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -885,7 +885,7 @@
         <v>62.56005859375</v>
       </c>
       <c r="V20">
-        <v>74.01000000000001</v>
+        <v>96.48</v>
       </c>
     </row>
     <row r="21" spans="1:22">
@@ -902,7 +902,7 @@
         <v>54.050048828125</v>
       </c>
       <c r="V21">
-        <v>68.84999999999999</v>
+        <v>85.7</v>
       </c>
     </row>
   </sheetData>

--- a/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao_20.xlsx
+++ b/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao_20.xlsx
@@ -76,7 +76,7 @@
     <t>Rodada 19</t>
   </si>
   <si>
-    <t>Parcial Rodada 2</t>
+    <t>Parcial Rodada 3</t>
   </si>
   <si>
     <t>time_id</t>
@@ -579,10 +579,10 @@
         <v>55.659912109375</v>
       </c>
       <c r="D2">
-        <v>55.659912109375</v>
-      </c>
-      <c r="V2">
-        <v>73.59999999999999</v>
+        <v>73.60009765625</v>
+      </c>
+      <c r="E2">
+        <v>73.60009765625</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -596,10 +596,10 @@
         <v>54.89990234375</v>
       </c>
       <c r="D3">
-        <v>54.89990234375</v>
-      </c>
-      <c r="V3">
-        <v>77.59999999999999</v>
+        <v>77.60009765625</v>
+      </c>
+      <c r="E3">
+        <v>77.60009765625</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -613,10 +613,10 @@
         <v>53.659912109375</v>
       </c>
       <c r="D4">
-        <v>53.659912109375</v>
-      </c>
-      <c r="V4">
-        <v>81.48</v>
+        <v>81.47998046875</v>
+      </c>
+      <c r="E4">
+        <v>81.47998046875</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -630,10 +630,7 @@
         <v>66.3701171875</v>
       </c>
       <c r="D5">
-        <v>66.3701171875</v>
-      </c>
-      <c r="V5">
-        <v>44.68</v>
+        <v>44.679931640625</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -647,10 +644,10 @@
         <v>68.06005859375</v>
       </c>
       <c r="D6">
-        <v>68.06005859375</v>
-      </c>
-      <c r="V6">
-        <v>82.18000000000001</v>
+        <v>82.18017578125</v>
+      </c>
+      <c r="E6">
+        <v>82.18017578125</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -664,10 +661,10 @@
         <v>60.60009765625</v>
       </c>
       <c r="D7">
-        <v>60.60009765625</v>
-      </c>
-      <c r="V7">
-        <v>75.88</v>
+        <v>75.8798828125</v>
+      </c>
+      <c r="E7">
+        <v>75.8798828125</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -681,10 +678,10 @@
         <v>47.860107421875</v>
       </c>
       <c r="D8">
-        <v>47.860107421875</v>
-      </c>
-      <c r="V8">
-        <v>90.59999999999999</v>
+        <v>90.60009765625</v>
+      </c>
+      <c r="E8">
+        <v>90.60009765625</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -698,10 +695,10 @@
         <v>47.860107421875</v>
       </c>
       <c r="D9">
-        <v>47.860107421875</v>
-      </c>
-      <c r="V9">
-        <v>72.18000000000001</v>
+        <v>72.18017578125</v>
+      </c>
+      <c r="E9">
+        <v>72.18017578125</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -715,10 +712,10 @@
         <v>55.659912109375</v>
       </c>
       <c r="D10">
-        <v>55.659912109375</v>
-      </c>
-      <c r="V10">
-        <v>55.78</v>
+        <v>55.780029296875</v>
+      </c>
+      <c r="E10">
+        <v>55.780029296875</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -732,10 +729,10 @@
         <v>71.9599609375</v>
       </c>
       <c r="D11">
-        <v>71.9599609375</v>
-      </c>
-      <c r="V11">
-        <v>66.68000000000001</v>
+        <v>66.68017578125</v>
+      </c>
+      <c r="E11">
+        <v>66.68017578125</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -749,10 +746,10 @@
         <v>83.2001953125</v>
       </c>
       <c r="D12">
-        <v>83.2001953125</v>
-      </c>
-      <c r="V12">
-        <v>98.7</v>
+        <v>98.7001953125</v>
+      </c>
+      <c r="E12">
+        <v>98.7001953125</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -765,9 +762,6 @@
       <c r="C13">
         <v>0</v>
       </c>
-      <c r="V13">
-        <v>95.41</v>
-      </c>
     </row>
     <row r="14" spans="1:22">
       <c r="A14" s="1">
@@ -780,10 +774,10 @@
         <v>67.16015625</v>
       </c>
       <c r="D14">
-        <v>67.16015625</v>
-      </c>
-      <c r="V14">
-        <v>86.45</v>
+        <v>86.4501953125</v>
+      </c>
+      <c r="E14">
+        <v>86.4501953125</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -797,10 +791,10 @@
         <v>61.56005859375</v>
       </c>
       <c r="D15">
-        <v>61.56005859375</v>
-      </c>
-      <c r="V15">
-        <v>83.48</v>
+        <v>83.47998046875</v>
+      </c>
+      <c r="E15">
+        <v>83.47998046875</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -814,13 +808,13 @@
         <v>56.050048828125</v>
       </c>
       <c r="D16">
-        <v>56.050048828125</v>
-      </c>
-      <c r="V16">
-        <v>70.3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22">
+        <v>70.43994140625</v>
+      </c>
+      <c r="E16">
+        <v>70.43994140625</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17" s="1">
         <v>19209079</v>
       </c>
@@ -831,13 +825,13 @@
         <v>63.56005859375</v>
       </c>
       <c r="D17">
-        <v>63.56005859375</v>
-      </c>
-      <c r="V17">
         <v>100.5</v>
       </c>
-    </row>
-    <row r="18" spans="1:22">
+      <c r="E17">
+        <v>100.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18" s="1">
         <v>19833277</v>
       </c>
@@ -848,13 +842,13 @@
         <v>64.5</v>
       </c>
       <c r="D18">
-        <v>64.5</v>
-      </c>
-      <c r="V18">
-        <v>75.68000000000001</v>
-      </c>
-    </row>
-    <row r="19" spans="1:22">
+        <v>75.68017578125</v>
+      </c>
+      <c r="E18">
+        <v>75.68017578125</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19" s="1">
         <v>20651178</v>
       </c>
@@ -865,13 +859,13 @@
         <v>61.159912109375</v>
       </c>
       <c r="D19">
-        <v>61.159912109375</v>
-      </c>
-      <c r="V19">
-        <v>71.18000000000001</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22">
+        <v>71.18017578125</v>
+      </c>
+      <c r="E19">
+        <v>71.18017578125</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20" s="1">
         <v>44810918</v>
       </c>
@@ -882,13 +876,13 @@
         <v>62.56005859375</v>
       </c>
       <c r="D20">
-        <v>62.56005859375</v>
-      </c>
-      <c r="V20">
-        <v>96.48</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22">
+        <v>96.47998046875</v>
+      </c>
+      <c r="E20">
+        <v>96.47998046875</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
       <c r="A21" s="1">
         <v>47775950</v>
       </c>
@@ -899,10 +893,10 @@
         <v>54.050048828125</v>
       </c>
       <c r="D21">
-        <v>54.050048828125</v>
-      </c>
-      <c r="V21">
-        <v>85.7</v>
+        <v>85.7001953125</v>
+      </c>
+      <c r="E21">
+        <v>85.7001953125</v>
       </c>
     </row>
   </sheetData>

--- a/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao_20.xlsx
+++ b/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao_20.xlsx
@@ -584,6 +584,9 @@
       <c r="E2">
         <v>73.60009765625</v>
       </c>
+      <c r="V2">
+        <v>41.97</v>
+      </c>
     </row>
     <row r="3" spans="1:22">
       <c r="A3" s="1">
@@ -601,6 +604,9 @@
       <c r="E3">
         <v>77.60009765625</v>
       </c>
+      <c r="V3">
+        <v>32.67</v>
+      </c>
     </row>
     <row r="4" spans="1:22">
       <c r="A4" s="1">
@@ -618,6 +624,9 @@
       <c r="E4">
         <v>81.47998046875</v>
       </c>
+      <c r="V4">
+        <v>38.07</v>
+      </c>
     </row>
     <row r="5" spans="1:22">
       <c r="A5" s="1">
@@ -632,6 +641,9 @@
       <c r="D5">
         <v>44.679931640625</v>
       </c>
+      <c r="V5">
+        <v>31.19</v>
+      </c>
     </row>
     <row r="6" spans="1:22">
       <c r="A6" s="1">
@@ -649,6 +661,9 @@
       <c r="E6">
         <v>82.18017578125</v>
       </c>
+      <c r="V6">
+        <v>45.17</v>
+      </c>
     </row>
     <row r="7" spans="1:22">
       <c r="A7" s="1">
@@ -666,6 +681,9 @@
       <c r="E7">
         <v>75.8798828125</v>
       </c>
+      <c r="V7">
+        <v>34.49</v>
+      </c>
     </row>
     <row r="8" spans="1:22">
       <c r="A8" s="1">
@@ -683,6 +701,9 @@
       <c r="E8">
         <v>90.60009765625</v>
       </c>
+      <c r="V8">
+        <v>31.67</v>
+      </c>
     </row>
     <row r="9" spans="1:22">
       <c r="A9" s="1">
@@ -700,6 +721,9 @@
       <c r="E9">
         <v>72.18017578125</v>
       </c>
+      <c r="V9">
+        <v>62.8</v>
+      </c>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" s="1">
@@ -717,6 +741,9 @@
       <c r="E10">
         <v>55.780029296875</v>
       </c>
+      <c r="V10">
+        <v>45.59</v>
+      </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="1">
@@ -734,6 +761,9 @@
       <c r="E11">
         <v>66.68017578125</v>
       </c>
+      <c r="V11">
+        <v>17.3</v>
+      </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1">
@@ -751,6 +781,9 @@
       <c r="E12">
         <v>98.7001953125</v>
       </c>
+      <c r="V12">
+        <v>31.8</v>
+      </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="1">
@@ -762,6 +795,9 @@
       <c r="C13">
         <v>0</v>
       </c>
+      <c r="V13">
+        <v>32.79</v>
+      </c>
     </row>
     <row r="14" spans="1:22">
       <c r="A14" s="1">
@@ -779,6 +815,9 @@
       <c r="E14">
         <v>86.4501953125</v>
       </c>
+      <c r="V14">
+        <v>44.97</v>
+      </c>
     </row>
     <row r="15" spans="1:22">
       <c r="A15" s="1">
@@ -796,6 +835,9 @@
       <c r="E15">
         <v>83.47998046875</v>
       </c>
+      <c r="V15">
+        <v>45.77</v>
+      </c>
     </row>
     <row r="16" spans="1:22">
       <c r="A16" s="1">
@@ -813,8 +855,11 @@
       <c r="E16">
         <v>70.43994140625</v>
       </c>
-    </row>
-    <row r="17" spans="1:5">
+      <c r="V16">
+        <v>20.29</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22">
       <c r="A17" s="1">
         <v>19209079</v>
       </c>
@@ -830,8 +875,11 @@
       <c r="E17">
         <v>100.5</v>
       </c>
-    </row>
-    <row r="18" spans="1:5">
+      <c r="V17">
+        <v>32.07</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22">
       <c r="A18" s="1">
         <v>19833277</v>
       </c>
@@ -847,8 +895,11 @@
       <c r="E18">
         <v>75.68017578125</v>
       </c>
-    </row>
-    <row r="19" spans="1:5">
+      <c r="V18">
+        <v>38.37</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22">
       <c r="A19" s="1">
         <v>20651178</v>
       </c>
@@ -864,8 +915,11 @@
       <c r="E19">
         <v>71.18017578125</v>
       </c>
-    </row>
-    <row r="20" spans="1:5">
+      <c r="V19">
+        <v>41.87</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22">
       <c r="A20" s="1">
         <v>44810918</v>
       </c>
@@ -881,8 +935,11 @@
       <c r="E20">
         <v>96.47998046875</v>
       </c>
-    </row>
-    <row r="21" spans="1:5">
+      <c r="V20">
+        <v>53.77</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22">
       <c r="A21" s="1">
         <v>47775950</v>
       </c>
@@ -897,6 +954,9 @@
       </c>
       <c r="E21">
         <v>85.7001953125</v>
+      </c>
+      <c r="V21">
+        <v>35.47</v>
       </c>
     </row>
   </sheetData>

--- a/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao_20.xlsx
+++ b/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao_20.xlsx
@@ -585,7 +585,7 @@
         <v>73.60009765625</v>
       </c>
       <c r="V2">
-        <v>41.97</v>
+        <v>99.26000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -605,7 +605,7 @@
         <v>77.60009765625</v>
       </c>
       <c r="V3">
-        <v>32.67</v>
+        <v>77.45999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -625,7 +625,7 @@
         <v>81.47998046875</v>
       </c>
       <c r="V4">
-        <v>38.07</v>
+        <v>78.45999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -642,7 +642,7 @@
         <v>44.679931640625</v>
       </c>
       <c r="V5">
-        <v>31.19</v>
+        <v>81.04000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -662,7 +662,7 @@
         <v>82.18017578125</v>
       </c>
       <c r="V6">
-        <v>45.17</v>
+        <v>105.76</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -682,7 +682,7 @@
         <v>75.8798828125</v>
       </c>
       <c r="V7">
-        <v>34.49</v>
+        <v>87.39</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -702,7 +702,7 @@
         <v>90.60009765625</v>
       </c>
       <c r="V8">
-        <v>31.67</v>
+        <v>85.26000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -722,7 +722,7 @@
         <v>72.18017578125</v>
       </c>
       <c r="V9">
-        <v>62.8</v>
+        <v>97.40000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -742,7 +742,7 @@
         <v>55.780029296875</v>
       </c>
       <c r="V10">
-        <v>45.59</v>
+        <v>88.14</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -762,7 +762,7 @@
         <v>66.68017578125</v>
       </c>
       <c r="V11">
-        <v>17.3</v>
+        <v>43.6</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -782,7 +782,7 @@
         <v>98.7001953125</v>
       </c>
       <c r="V12">
-        <v>31.8</v>
+        <v>108.2</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -796,7 +796,7 @@
         <v>0</v>
       </c>
       <c r="V13">
-        <v>32.79</v>
+        <v>56.24</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -816,7 +816,7 @@
         <v>86.4501953125</v>
       </c>
       <c r="V14">
-        <v>44.97</v>
+        <v>63.56</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -836,7 +836,7 @@
         <v>83.47998046875</v>
       </c>
       <c r="V15">
-        <v>45.77</v>
+        <v>90.45999999999999</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -856,7 +856,7 @@
         <v>70.43994140625</v>
       </c>
       <c r="V16">
-        <v>20.29</v>
+        <v>70.04000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -876,7 +876,7 @@
         <v>100.5</v>
       </c>
       <c r="V17">
-        <v>32.07</v>
+        <v>91.66</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -896,7 +896,7 @@
         <v>75.68017578125</v>
       </c>
       <c r="V18">
-        <v>38.37</v>
+        <v>73.26000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -916,7 +916,7 @@
         <v>71.18017578125</v>
       </c>
       <c r="V19">
-        <v>41.87</v>
+        <v>72.26000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -936,7 +936,7 @@
         <v>96.47998046875</v>
       </c>
       <c r="V20">
-        <v>53.77</v>
+        <v>87.45999999999999</v>
       </c>
     </row>
     <row r="21" spans="1:22">
@@ -956,7 +956,7 @@
         <v>85.7001953125</v>
       </c>
       <c r="V21">
-        <v>35.47</v>
+        <v>65.66</v>
       </c>
     </row>
   </sheetData>

--- a/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao_20.xlsx
+++ b/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao_20.xlsx
@@ -76,7 +76,7 @@
     <t>Rodada 19</t>
   </si>
   <si>
-    <t>Parcial Rodada 3</t>
+    <t>Parcial Rodada 4</t>
   </si>
   <si>
     <t>time_id</t>
@@ -582,10 +582,10 @@
         <v>73.60009765625</v>
       </c>
       <c r="E2">
-        <v>73.60009765625</v>
-      </c>
-      <c r="V2">
-        <v>99.26000000000001</v>
+        <v>100.06005859375</v>
+      </c>
+      <c r="F2">
+        <v>100.06005859375</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -602,10 +602,10 @@
         <v>77.60009765625</v>
       </c>
       <c r="E3">
-        <v>77.60009765625</v>
-      </c>
-      <c r="V3">
-        <v>77.45999999999999</v>
+        <v>78.259765625</v>
+      </c>
+      <c r="F3">
+        <v>78.259765625</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -622,10 +622,10 @@
         <v>81.47998046875</v>
       </c>
       <c r="E4">
-        <v>81.47998046875</v>
-      </c>
-      <c r="V4">
-        <v>78.45999999999999</v>
+        <v>79.259765625</v>
+      </c>
+      <c r="F4">
+        <v>79.259765625</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -641,9 +641,6 @@
       <c r="D5">
         <v>44.679931640625</v>
       </c>
-      <c r="V5">
-        <v>81.04000000000001</v>
-      </c>
     </row>
     <row r="6" spans="1:22">
       <c r="A6" s="1">
@@ -659,10 +656,10 @@
         <v>82.18017578125</v>
       </c>
       <c r="E6">
-        <v>82.18017578125</v>
-      </c>
-      <c r="V6">
-        <v>105.76</v>
+        <v>105.759765625</v>
+      </c>
+      <c r="F6">
+        <v>105.759765625</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -679,10 +676,10 @@
         <v>75.8798828125</v>
       </c>
       <c r="E7">
-        <v>75.8798828125</v>
-      </c>
-      <c r="V7">
-        <v>87.39</v>
+        <v>87.39013671875</v>
+      </c>
+      <c r="F7">
+        <v>87.39013671875</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -699,10 +696,10 @@
         <v>90.60009765625</v>
       </c>
       <c r="E8">
-        <v>90.60009765625</v>
-      </c>
-      <c r="V8">
-        <v>85.26000000000001</v>
+        <v>84.56005859375</v>
+      </c>
+      <c r="F8">
+        <v>84.56005859375</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -719,10 +716,10 @@
         <v>72.18017578125</v>
       </c>
       <c r="E9">
-        <v>72.18017578125</v>
-      </c>
-      <c r="V9">
-        <v>97.40000000000001</v>
+        <v>97.39990234375</v>
+      </c>
+      <c r="F9">
+        <v>97.39990234375</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -739,10 +736,10 @@
         <v>55.780029296875</v>
       </c>
       <c r="E10">
-        <v>55.780029296875</v>
-      </c>
-      <c r="V10">
-        <v>88.14</v>
+        <v>88.93994140625</v>
+      </c>
+      <c r="F10">
+        <v>88.93994140625</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -759,10 +756,7 @@
         <v>66.68017578125</v>
       </c>
       <c r="E11">
-        <v>66.68017578125</v>
-      </c>
-      <c r="V11">
-        <v>43.6</v>
+        <v>42.14990234375</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -779,10 +773,10 @@
         <v>98.7001953125</v>
       </c>
       <c r="E12">
-        <v>98.7001953125</v>
-      </c>
-      <c r="V12">
-        <v>108.2</v>
+        <v>109</v>
+      </c>
+      <c r="F12">
+        <v>109</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -795,9 +789,6 @@
       <c r="C13">
         <v>0</v>
       </c>
-      <c r="V13">
-        <v>56.24</v>
-      </c>
     </row>
     <row r="14" spans="1:22">
       <c r="A14" s="1">
@@ -813,10 +804,10 @@
         <v>86.4501953125</v>
       </c>
       <c r="E14">
-        <v>86.4501953125</v>
-      </c>
-      <c r="V14">
-        <v>63.56</v>
+        <v>64.35986328125</v>
+      </c>
+      <c r="F14">
+        <v>64.35986328125</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -833,10 +824,10 @@
         <v>83.47998046875</v>
       </c>
       <c r="E15">
-        <v>83.47998046875</v>
-      </c>
-      <c r="V15">
-        <v>90.45999999999999</v>
+        <v>90.4599609375</v>
+      </c>
+      <c r="F15">
+        <v>90.4599609375</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -853,13 +844,13 @@
         <v>70.43994140625</v>
       </c>
       <c r="E16">
-        <v>70.43994140625</v>
-      </c>
-      <c r="V16">
-        <v>70.04000000000001</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22">
+        <v>71.64013671875</v>
+      </c>
+      <c r="F16">
+        <v>71.64013671875</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17" s="1">
         <v>19209079</v>
       </c>
@@ -873,13 +864,13 @@
         <v>100.5</v>
       </c>
       <c r="E17">
-        <v>100.5</v>
-      </c>
-      <c r="V17">
-        <v>91.66</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22">
+        <v>91.66015625</v>
+      </c>
+      <c r="F17">
+        <v>91.66015625</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18" s="1">
         <v>19833277</v>
       </c>
@@ -893,13 +884,13 @@
         <v>75.68017578125</v>
       </c>
       <c r="E18">
-        <v>75.68017578125</v>
-      </c>
-      <c r="V18">
-        <v>73.26000000000001</v>
-      </c>
-    </row>
-    <row r="19" spans="1:22">
+        <v>73.259765625</v>
+      </c>
+      <c r="F18">
+        <v>73.259765625</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19" s="1">
         <v>20651178</v>
       </c>
@@ -913,13 +904,13 @@
         <v>71.18017578125</v>
       </c>
       <c r="E19">
-        <v>71.18017578125</v>
-      </c>
-      <c r="V19">
-        <v>72.26000000000001</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22">
+        <v>73.06005859375</v>
+      </c>
+      <c r="F19">
+        <v>73.06005859375</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20" s="1">
         <v>44810918</v>
       </c>
@@ -933,13 +924,13 @@
         <v>96.47998046875</v>
       </c>
       <c r="E20">
-        <v>96.47998046875</v>
-      </c>
-      <c r="V20">
-        <v>87.45999999999999</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22">
+        <v>87.4599609375</v>
+      </c>
+      <c r="F20">
+        <v>87.4599609375</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
       <c r="A21" s="1">
         <v>47775950</v>
       </c>
@@ -953,10 +944,10 @@
         <v>85.7001953125</v>
       </c>
       <c r="E21">
-        <v>85.7001953125</v>
-      </c>
-      <c r="V21">
-        <v>65.66</v>
+        <v>65.66015625</v>
+      </c>
+      <c r="F21">
+        <v>65.66015625</v>
       </c>
     </row>
   </sheetData>

--- a/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao_20.xlsx
+++ b/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao_20.xlsx
@@ -587,6 +587,9 @@
       <c r="F2">
         <v>100.06005859375</v>
       </c>
+      <c r="V2">
+        <v>40.2</v>
+      </c>
     </row>
     <row r="3" spans="1:22">
       <c r="A3" s="1">
@@ -607,6 +610,9 @@
       <c r="F3">
         <v>78.259765625</v>
       </c>
+      <c r="V3">
+        <v>41.7</v>
+      </c>
     </row>
     <row r="4" spans="1:22">
       <c r="A4" s="1">
@@ -627,6 +633,9 @@
       <c r="F4">
         <v>79.259765625</v>
       </c>
+      <c r="V4">
+        <v>59.53</v>
+      </c>
     </row>
     <row r="5" spans="1:22">
       <c r="A5" s="1">
@@ -641,6 +650,9 @@
       <c r="D5">
         <v>44.679931640625</v>
       </c>
+      <c r="V5">
+        <v>29.1</v>
+      </c>
     </row>
     <row r="6" spans="1:22">
       <c r="A6" s="1">
@@ -661,6 +673,9 @@
       <c r="F6">
         <v>105.759765625</v>
       </c>
+      <c r="V6">
+        <v>43.8</v>
+      </c>
     </row>
     <row r="7" spans="1:22">
       <c r="A7" s="1">
@@ -681,6 +696,9 @@
       <c r="F7">
         <v>87.39013671875</v>
       </c>
+      <c r="V7">
+        <v>29.3</v>
+      </c>
     </row>
     <row r="8" spans="1:22">
       <c r="A8" s="1">
@@ -701,6 +719,9 @@
       <c r="F8">
         <v>84.56005859375</v>
       </c>
+      <c r="V8">
+        <v>44.4</v>
+      </c>
     </row>
     <row r="9" spans="1:22">
       <c r="A9" s="1">
@@ -721,6 +742,9 @@
       <c r="F9">
         <v>97.39990234375</v>
       </c>
+      <c r="V9">
+        <v>65.05</v>
+      </c>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" s="1">
@@ -741,6 +765,9 @@
       <c r="F10">
         <v>88.93994140625</v>
       </c>
+      <c r="V10">
+        <v>56.8</v>
+      </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="1">
@@ -758,6 +785,9 @@
       <c r="E11">
         <v>42.14990234375</v>
       </c>
+      <c r="V11">
+        <v>32.14</v>
+      </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1">
@@ -778,6 +808,9 @@
       <c r="F12">
         <v>109</v>
       </c>
+      <c r="V12">
+        <v>61.45</v>
+      </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="1">
@@ -789,6 +822,9 @@
       <c r="C13">
         <v>0</v>
       </c>
+      <c r="V13">
+        <v>48.44</v>
+      </c>
     </row>
     <row r="14" spans="1:22">
       <c r="A14" s="1">
@@ -809,6 +845,9 @@
       <c r="F14">
         <v>64.35986328125</v>
       </c>
+      <c r="V14">
+        <v>54.43</v>
+      </c>
     </row>
     <row r="15" spans="1:22">
       <c r="A15" s="1">
@@ -829,6 +868,9 @@
       <c r="F15">
         <v>90.4599609375</v>
       </c>
+      <c r="V15">
+        <v>50.22</v>
+      </c>
     </row>
     <row r="16" spans="1:22">
       <c r="A16" s="1">
@@ -849,8 +891,11 @@
       <c r="F16">
         <v>71.64013671875</v>
       </c>
-    </row>
-    <row r="17" spans="1:6">
+      <c r="V16">
+        <v>45.3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22">
       <c r="A17" s="1">
         <v>19209079</v>
       </c>
@@ -869,8 +914,11 @@
       <c r="F17">
         <v>91.66015625</v>
       </c>
-    </row>
-    <row r="18" spans="1:6">
+      <c r="V17">
+        <v>39.55</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22">
       <c r="A18" s="1">
         <v>19833277</v>
       </c>
@@ -889,8 +937,11 @@
       <c r="F18">
         <v>73.259765625</v>
       </c>
-    </row>
-    <row r="19" spans="1:6">
+      <c r="V18">
+        <v>40.15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22">
       <c r="A19" s="1">
         <v>20651178</v>
       </c>
@@ -909,8 +960,11 @@
       <c r="F19">
         <v>73.06005859375</v>
       </c>
-    </row>
-    <row r="20" spans="1:6">
+      <c r="V19">
+        <v>38.55</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22">
       <c r="A20" s="1">
         <v>44810918</v>
       </c>
@@ -929,8 +983,11 @@
       <c r="F20">
         <v>87.4599609375</v>
       </c>
-    </row>
-    <row r="21" spans="1:6">
+      <c r="V20">
+        <v>44.1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22">
       <c r="A21" s="1">
         <v>47775950</v>
       </c>
@@ -948,6 +1005,9 @@
       </c>
       <c r="F21">
         <v>65.66015625</v>
+      </c>
+      <c r="V21">
+        <v>37.65</v>
       </c>
     </row>
   </sheetData>

--- a/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao_20.xlsx
+++ b/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao_20.xlsx
@@ -588,7 +588,7 @@
         <v>100.06005859375</v>
       </c>
       <c r="V2">
-        <v>40.2</v>
+        <v>43.55</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -611,7 +611,7 @@
         <v>78.259765625</v>
       </c>
       <c r="V3">
-        <v>41.7</v>
+        <v>43.35</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -634,7 +634,7 @@
         <v>79.259765625</v>
       </c>
       <c r="V4">
-        <v>59.53</v>
+        <v>68.73</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -651,7 +651,7 @@
         <v>44.679931640625</v>
       </c>
       <c r="V5">
-        <v>29.1</v>
+        <v>44.35</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -674,7 +674,7 @@
         <v>105.759765625</v>
       </c>
       <c r="V6">
-        <v>43.8</v>
+        <v>46.65</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -697,7 +697,7 @@
         <v>87.39013671875</v>
       </c>
       <c r="V7">
-        <v>29.3</v>
+        <v>37.16</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -720,7 +720,7 @@
         <v>84.56005859375</v>
       </c>
       <c r="V8">
-        <v>44.4</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -743,7 +743,7 @@
         <v>97.39990234375</v>
       </c>
       <c r="V9">
-        <v>65.05</v>
+        <v>81.65000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -766,7 +766,7 @@
         <v>88.93994140625</v>
       </c>
       <c r="V10">
-        <v>56.8</v>
+        <v>59.41</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -786,7 +786,7 @@
         <v>42.14990234375</v>
       </c>
       <c r="V11">
-        <v>32.14</v>
+        <v>30.8</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -809,7 +809,7 @@
         <v>109</v>
       </c>
       <c r="V12">
-        <v>61.45</v>
+        <v>75.95999999999999</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -823,7 +823,7 @@
         <v>0</v>
       </c>
       <c r="V13">
-        <v>48.44</v>
+        <v>47.84</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -846,7 +846,7 @@
         <v>64.35986328125</v>
       </c>
       <c r="V14">
-        <v>54.43</v>
+        <v>61.13</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -869,7 +869,7 @@
         <v>90.4599609375</v>
       </c>
       <c r="V15">
-        <v>50.22</v>
+        <v>56.68</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -892,7 +892,7 @@
         <v>71.64013671875</v>
       </c>
       <c r="V16">
-        <v>45.3</v>
+        <v>56.16</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -915,7 +915,7 @@
         <v>91.66015625</v>
       </c>
       <c r="V17">
-        <v>39.55</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -938,7 +938,7 @@
         <v>73.259765625</v>
       </c>
       <c r="V18">
-        <v>40.15</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -961,7 +961,7 @@
         <v>73.06005859375</v>
       </c>
       <c r="V19">
-        <v>38.55</v>
+        <v>42.56</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -984,7 +984,7 @@
         <v>87.4599609375</v>
       </c>
       <c r="V20">
-        <v>44.1</v>
+        <v>58</v>
       </c>
     </row>
     <row r="21" spans="1:22">
@@ -1007,7 +1007,7 @@
         <v>65.66015625</v>
       </c>
       <c r="V21">
-        <v>37.65</v>
+        <v>47.9</v>
       </c>
     </row>
   </sheetData>

--- a/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao_20.xlsx
+++ b/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao_20.xlsx
@@ -588,7 +588,7 @@
         <v>100.06005859375</v>
       </c>
       <c r="V2">
-        <v>43.55</v>
+        <v>62.75</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -611,7 +611,7 @@
         <v>78.259765625</v>
       </c>
       <c r="V3">
-        <v>43.35</v>
+        <v>45.55</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -634,7 +634,7 @@
         <v>79.259765625</v>
       </c>
       <c r="V4">
-        <v>68.73</v>
+        <v>86.43000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -651,7 +651,7 @@
         <v>44.679931640625</v>
       </c>
       <c r="V5">
-        <v>44.35</v>
+        <v>61.35</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -674,7 +674,7 @@
         <v>105.759765625</v>
       </c>
       <c r="V6">
-        <v>46.65</v>
+        <v>65.15000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -697,7 +697,7 @@
         <v>87.39013671875</v>
       </c>
       <c r="V7">
-        <v>37.16</v>
+        <v>42.56</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -720,7 +720,7 @@
         <v>84.56005859375</v>
       </c>
       <c r="V8">
-        <v>47.5</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -809,7 +809,7 @@
         <v>109</v>
       </c>
       <c r="V12">
-        <v>75.95999999999999</v>
+        <v>121.76</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -823,7 +823,7 @@
         <v>0</v>
       </c>
       <c r="V13">
-        <v>47.84</v>
+        <v>72.23999999999999</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -869,7 +869,7 @@
         <v>90.4599609375</v>
       </c>
       <c r="V15">
-        <v>56.68</v>
+        <v>76.06</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -892,7 +892,7 @@
         <v>71.64013671875</v>
       </c>
       <c r="V16">
-        <v>56.16</v>
+        <v>56.36</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -915,7 +915,7 @@
         <v>91.66015625</v>
       </c>
       <c r="V17">
-        <v>51.6</v>
+        <v>77.23</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -938,7 +938,7 @@
         <v>73.259765625</v>
       </c>
       <c r="V18">
-        <v>43</v>
+        <v>49.43</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -984,7 +984,7 @@
         <v>87.4599609375</v>
       </c>
       <c r="V20">
-        <v>58</v>
+        <v>81.43000000000001</v>
       </c>
     </row>
     <row r="21" spans="1:22">
@@ -1007,7 +1007,7 @@
         <v>65.66015625</v>
       </c>
       <c r="V21">
-        <v>47.9</v>
+        <v>49.45</v>
       </c>
     </row>
   </sheetData>

--- a/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao_20.xlsx
+++ b/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao_20.xlsx
@@ -76,7 +76,7 @@
     <t>Rodada 19</t>
   </si>
   <si>
-    <t>Parcial Rodada 4</t>
+    <t>Parcial Rodada 5</t>
   </si>
   <si>
     <t>time_id</t>
@@ -585,9 +585,9 @@
         <v>100.06005859375</v>
       </c>
       <c r="F2">
-        <v>100.06005859375</v>
-      </c>
-      <c r="V2">
+        <v>62.75</v>
+      </c>
+      <c r="G2">
         <v>62.75</v>
       </c>
     </row>
@@ -608,10 +608,10 @@
         <v>78.259765625</v>
       </c>
       <c r="F3">
-        <v>78.259765625</v>
-      </c>
-      <c r="V3">
-        <v>45.55</v>
+        <v>45.550048828125</v>
+      </c>
+      <c r="G3">
+        <v>45.550048828125</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -631,10 +631,10 @@
         <v>79.259765625</v>
       </c>
       <c r="F4">
-        <v>79.259765625</v>
-      </c>
-      <c r="V4">
-        <v>86.43000000000001</v>
+        <v>86.43017578125</v>
+      </c>
+      <c r="G4">
+        <v>86.43017578125</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -650,9 +650,6 @@
       <c r="D5">
         <v>44.679931640625</v>
       </c>
-      <c r="V5">
-        <v>61.35</v>
-      </c>
     </row>
     <row r="6" spans="1:22">
       <c r="A6" s="1">
@@ -671,10 +668,10 @@
         <v>105.759765625</v>
       </c>
       <c r="F6">
-        <v>105.759765625</v>
-      </c>
-      <c r="V6">
-        <v>65.15000000000001</v>
+        <v>65.14990234375</v>
+      </c>
+      <c r="G6">
+        <v>65.14990234375</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -694,10 +691,10 @@
         <v>87.39013671875</v>
       </c>
       <c r="F7">
-        <v>87.39013671875</v>
-      </c>
-      <c r="V7">
-        <v>42.56</v>
+        <v>42.56005859375</v>
+      </c>
+      <c r="G7">
+        <v>42.56005859375</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -717,9 +714,9 @@
         <v>84.56005859375</v>
       </c>
       <c r="F8">
-        <v>84.56005859375</v>
-      </c>
-      <c r="V8">
+        <v>55</v>
+      </c>
+      <c r="G8">
         <v>55</v>
       </c>
     </row>
@@ -740,10 +737,10 @@
         <v>97.39990234375</v>
       </c>
       <c r="F9">
-        <v>97.39990234375</v>
-      </c>
-      <c r="V9">
-        <v>81.65000000000001</v>
+        <v>81.64990234375</v>
+      </c>
+      <c r="G9">
+        <v>81.64990234375</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -763,10 +760,10 @@
         <v>88.93994140625</v>
       </c>
       <c r="F10">
-        <v>88.93994140625</v>
-      </c>
-      <c r="V10">
-        <v>59.41</v>
+        <v>59.409912109375</v>
+      </c>
+      <c r="G10">
+        <v>59.409912109375</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -785,9 +782,6 @@
       <c r="E11">
         <v>42.14990234375</v>
       </c>
-      <c r="V11">
-        <v>30.8</v>
-      </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1">
@@ -806,10 +800,10 @@
         <v>109</v>
       </c>
       <c r="F12">
-        <v>109</v>
-      </c>
-      <c r="V12">
-        <v>121.76</v>
+        <v>121.759765625</v>
+      </c>
+      <c r="G12">
+        <v>121.759765625</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -822,9 +816,6 @@
       <c r="C13">
         <v>0</v>
       </c>
-      <c r="V13">
-        <v>72.23999999999999</v>
-      </c>
     </row>
     <row r="14" spans="1:22">
       <c r="A14" s="1">
@@ -843,10 +834,10 @@
         <v>64.35986328125</v>
       </c>
       <c r="F14">
-        <v>64.35986328125</v>
-      </c>
-      <c r="V14">
-        <v>61.13</v>
+        <v>61.1298828125</v>
+      </c>
+      <c r="G14">
+        <v>61.1298828125</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -866,10 +857,10 @@
         <v>90.4599609375</v>
       </c>
       <c r="F15">
-        <v>90.4599609375</v>
-      </c>
-      <c r="V15">
-        <v>76.06</v>
+        <v>76.06005859375</v>
+      </c>
+      <c r="G15">
+        <v>76.06005859375</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -889,13 +880,13 @@
         <v>71.64013671875</v>
       </c>
       <c r="F16">
-        <v>71.64013671875</v>
-      </c>
-      <c r="V16">
-        <v>56.36</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22">
+        <v>56.360107421875</v>
+      </c>
+      <c r="G16">
+        <v>56.360107421875</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
       <c r="A17" s="1">
         <v>19209079</v>
       </c>
@@ -912,13 +903,13 @@
         <v>91.66015625</v>
       </c>
       <c r="F17">
-        <v>91.66015625</v>
-      </c>
-      <c r="V17">
-        <v>77.23</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22">
+        <v>77.22998046875</v>
+      </c>
+      <c r="G17">
+        <v>77.22998046875</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
       <c r="A18" s="1">
         <v>19833277</v>
       </c>
@@ -935,13 +926,13 @@
         <v>73.259765625</v>
       </c>
       <c r="F18">
-        <v>73.259765625</v>
-      </c>
-      <c r="V18">
-        <v>49.43</v>
-      </c>
-    </row>
-    <row r="19" spans="1:22">
+        <v>49.429931640625</v>
+      </c>
+      <c r="G18">
+        <v>49.429931640625</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="A19" s="1">
         <v>20651178</v>
       </c>
@@ -958,13 +949,10 @@
         <v>73.06005859375</v>
       </c>
       <c r="F19">
-        <v>73.06005859375</v>
-      </c>
-      <c r="V19">
-        <v>42.56</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22">
+        <v>42.56005859375</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
       <c r="A20" s="1">
         <v>44810918</v>
       </c>
@@ -981,13 +969,13 @@
         <v>87.4599609375</v>
       </c>
       <c r="F20">
-        <v>87.4599609375</v>
-      </c>
-      <c r="V20">
-        <v>81.43000000000001</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22">
+        <v>81.43017578125</v>
+      </c>
+      <c r="G20">
+        <v>81.43017578125</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
       <c r="A21" s="1">
         <v>47775950</v>
       </c>
@@ -1004,10 +992,10 @@
         <v>65.66015625</v>
       </c>
       <c r="F21">
-        <v>65.66015625</v>
-      </c>
-      <c r="V21">
-        <v>49.45</v>
+        <v>49.449951171875</v>
+      </c>
+      <c r="G21">
+        <v>49.449951171875</v>
       </c>
     </row>
   </sheetData>

--- a/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao_20.xlsx
+++ b/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao_20.xlsx
@@ -124,7 +124,7 @@
     <t>GrioTeam</t>
   </si>
   <si>
-    <t>GE Bebum</t>
+    <t>GE Xavanchesteer</t>
   </si>
   <si>
     <t xml:space="preserve">bugredasmissões </t>
@@ -590,6 +590,9 @@
       <c r="G2">
         <v>62.75</v>
       </c>
+      <c r="V2">
+        <v>6.7</v>
+      </c>
     </row>
     <row r="3" spans="1:22">
       <c r="A3" s="1">
@@ -613,6 +616,9 @@
       <c r="G3">
         <v>45.550048828125</v>
       </c>
+      <c r="V3">
+        <v>17.9</v>
+      </c>
     </row>
     <row r="4" spans="1:22">
       <c r="A4" s="1">
@@ -636,6 +642,9 @@
       <c r="G4">
         <v>86.43017578125</v>
       </c>
+      <c r="V4">
+        <v>25.7</v>
+      </c>
     </row>
     <row r="5" spans="1:22">
       <c r="A5" s="1">
@@ -650,6 +659,9 @@
       <c r="D5">
         <v>44.679931640625</v>
       </c>
+      <c r="V5">
+        <v>15.2</v>
+      </c>
     </row>
     <row r="6" spans="1:22">
       <c r="A6" s="1">
@@ -673,6 +685,9 @@
       <c r="G6">
         <v>65.14990234375</v>
       </c>
+      <c r="V6">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="7" spans="1:22">
       <c r="A7" s="1">
@@ -696,6 +711,9 @@
       <c r="G7">
         <v>42.56005859375</v>
       </c>
+      <c r="V7">
+        <v>7.4</v>
+      </c>
     </row>
     <row r="8" spans="1:22">
       <c r="A8" s="1">
@@ -719,6 +737,9 @@
       <c r="G8">
         <v>55</v>
       </c>
+      <c r="V8">
+        <v>17.6</v>
+      </c>
     </row>
     <row r="9" spans="1:22">
       <c r="A9" s="1">
@@ -742,6 +763,9 @@
       <c r="G9">
         <v>81.64990234375</v>
       </c>
+      <c r="V9">
+        <v>13.8</v>
+      </c>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" s="1">
@@ -765,6 +789,9 @@
       <c r="G10">
         <v>59.409912109375</v>
       </c>
+      <c r="V10">
+        <v>10.7</v>
+      </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="1">
@@ -782,6 +809,9 @@
       <c r="E11">
         <v>42.14990234375</v>
       </c>
+      <c r="V11">
+        <v>39.15</v>
+      </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1">
@@ -805,6 +835,9 @@
       <c r="G12">
         <v>121.759765625</v>
       </c>
+      <c r="V12">
+        <v>27.6</v>
+      </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="1">
@@ -816,6 +849,9 @@
       <c r="C13">
         <v>0</v>
       </c>
+      <c r="V13">
+        <v>9.75</v>
+      </c>
     </row>
     <row r="14" spans="1:22">
       <c r="A14" s="1">
@@ -839,6 +875,9 @@
       <c r="G14">
         <v>61.1298828125</v>
       </c>
+      <c r="V14">
+        <v>25.9</v>
+      </c>
     </row>
     <row r="15" spans="1:22">
       <c r="A15" s="1">
@@ -862,6 +901,9 @@
       <c r="G15">
         <v>76.06005859375</v>
       </c>
+      <c r="V15">
+        <v>2.2</v>
+      </c>
     </row>
     <row r="16" spans="1:22">
       <c r="A16" s="1">
@@ -885,8 +927,11 @@
       <c r="G16">
         <v>56.360107421875</v>
       </c>
-    </row>
-    <row r="17" spans="1:7">
+      <c r="V16">
+        <v>28.89</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22">
       <c r="A17" s="1">
         <v>19209079</v>
       </c>
@@ -908,8 +953,11 @@
       <c r="G17">
         <v>77.22998046875</v>
       </c>
-    </row>
-    <row r="18" spans="1:7">
+      <c r="V17">
+        <v>22.7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22">
       <c r="A18" s="1">
         <v>19833277</v>
       </c>
@@ -931,8 +979,11 @@
       <c r="G18">
         <v>49.429931640625</v>
       </c>
-    </row>
-    <row r="19" spans="1:7">
+      <c r="V18">
+        <v>22.7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22">
       <c r="A19" s="1">
         <v>20651178</v>
       </c>
@@ -951,8 +1002,11 @@
       <c r="F19">
         <v>42.56005859375</v>
       </c>
-    </row>
-    <row r="20" spans="1:7">
+      <c r="V19">
+        <v>17.9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22">
       <c r="A20" s="1">
         <v>44810918</v>
       </c>
@@ -974,8 +1028,11 @@
       <c r="G20">
         <v>81.43017578125</v>
       </c>
-    </row>
-    <row r="21" spans="1:7">
+      <c r="V20">
+        <v>11.7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22">
       <c r="A21" s="1">
         <v>47775950</v>
       </c>
@@ -996,6 +1053,9 @@
       </c>
       <c r="G21">
         <v>49.449951171875</v>
+      </c>
+      <c r="V21">
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao_20.xlsx
+++ b/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao_20.xlsx
@@ -76,7 +76,7 @@
     <t>Rodada 19</t>
   </si>
   <si>
-    <t>Parcial Rodada 5</t>
+    <t>Parcial Rodada 6</t>
   </si>
   <si>
     <t>time_id</t>
@@ -588,10 +588,10 @@
         <v>62.75</v>
       </c>
       <c r="G2">
-        <v>62.75</v>
-      </c>
-      <c r="V2">
-        <v>6.7</v>
+        <v>77.22021484375</v>
+      </c>
+      <c r="H2">
+        <v>77.22021484375</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -614,10 +614,10 @@
         <v>45.550048828125</v>
       </c>
       <c r="G3">
-        <v>45.550048828125</v>
-      </c>
-      <c r="V3">
-        <v>17.9</v>
+        <v>77.6201171875</v>
+      </c>
+      <c r="H3">
+        <v>77.6201171875</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -640,10 +640,10 @@
         <v>86.43017578125</v>
       </c>
       <c r="G4">
-        <v>86.43017578125</v>
-      </c>
-      <c r="V4">
-        <v>25.7</v>
+        <v>86.419921875</v>
+      </c>
+      <c r="H4">
+        <v>86.419921875</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -659,9 +659,6 @@
       <c r="D5">
         <v>44.679931640625</v>
       </c>
-      <c r="V5">
-        <v>15.2</v>
-      </c>
     </row>
     <row r="6" spans="1:22">
       <c r="A6" s="1">
@@ -683,10 +680,10 @@
         <v>65.14990234375</v>
       </c>
       <c r="G6">
-        <v>65.14990234375</v>
-      </c>
-      <c r="V6">
-        <v>22.3</v>
+        <v>93.02001953125</v>
+      </c>
+      <c r="H6">
+        <v>93.02001953125</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -709,10 +706,10 @@
         <v>42.56005859375</v>
       </c>
       <c r="G7">
-        <v>42.56005859375</v>
-      </c>
-      <c r="V7">
-        <v>7.4</v>
+        <v>49.77001953125</v>
+      </c>
+      <c r="H7">
+        <v>49.77001953125</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -735,10 +732,10 @@
         <v>55</v>
       </c>
       <c r="G8">
-        <v>55</v>
-      </c>
-      <c r="V8">
-        <v>17.6</v>
+        <v>63.8701171875</v>
+      </c>
+      <c r="H8">
+        <v>63.8701171875</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -761,10 +758,10 @@
         <v>81.64990234375</v>
       </c>
       <c r="G9">
-        <v>81.64990234375</v>
-      </c>
-      <c r="V9">
-        <v>13.8</v>
+        <v>84.81982421875</v>
+      </c>
+      <c r="H9">
+        <v>84.81982421875</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -787,10 +784,10 @@
         <v>59.409912109375</v>
       </c>
       <c r="G10">
-        <v>59.409912109375</v>
-      </c>
-      <c r="V10">
-        <v>10.7</v>
+        <v>84.6201171875</v>
+      </c>
+      <c r="H10">
+        <v>84.6201171875</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -809,9 +806,6 @@
       <c r="E11">
         <v>42.14990234375</v>
       </c>
-      <c r="V11">
-        <v>39.15</v>
-      </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1">
@@ -833,10 +827,10 @@
         <v>121.759765625</v>
       </c>
       <c r="G12">
-        <v>121.759765625</v>
-      </c>
-      <c r="V12">
-        <v>27.6</v>
+        <v>93.06982421875</v>
+      </c>
+      <c r="H12">
+        <v>93.06982421875</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -849,9 +843,6 @@
       <c r="C13">
         <v>0</v>
       </c>
-      <c r="V13">
-        <v>9.75</v>
-      </c>
     </row>
     <row r="14" spans="1:22">
       <c r="A14" s="1">
@@ -873,10 +864,10 @@
         <v>61.1298828125</v>
       </c>
       <c r="G14">
-        <v>61.1298828125</v>
-      </c>
-      <c r="V14">
-        <v>25.9</v>
+        <v>72.759765625</v>
+      </c>
+      <c r="H14">
+        <v>72.759765625</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -899,10 +890,7 @@
         <v>76.06005859375</v>
       </c>
       <c r="G15">
-        <v>76.06005859375</v>
-      </c>
-      <c r="V15">
-        <v>2.2</v>
+        <v>41.169921875</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -925,13 +913,13 @@
         <v>56.360107421875</v>
       </c>
       <c r="G16">
-        <v>56.360107421875</v>
-      </c>
-      <c r="V16">
-        <v>28.89</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22">
+        <v>88.240234375</v>
+      </c>
+      <c r="H16">
+        <v>88.240234375</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" s="1">
         <v>19209079</v>
       </c>
@@ -951,13 +939,13 @@
         <v>77.22998046875</v>
       </c>
       <c r="G17">
-        <v>77.22998046875</v>
-      </c>
-      <c r="V17">
-        <v>22.7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22">
+        <v>78.47021484375</v>
+      </c>
+      <c r="H17">
+        <v>78.47021484375</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" s="1">
         <v>19833277</v>
       </c>
@@ -977,13 +965,13 @@
         <v>49.429931640625</v>
       </c>
       <c r="G18">
-        <v>49.429931640625</v>
-      </c>
-      <c r="V18">
-        <v>22.7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:22">
+        <v>87.919921875</v>
+      </c>
+      <c r="H18">
+        <v>87.919921875</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" s="1">
         <v>20651178</v>
       </c>
@@ -1002,11 +990,8 @@
       <c r="F19">
         <v>42.56005859375</v>
       </c>
-      <c r="V19">
-        <v>17.9</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22">
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" s="1">
         <v>44810918</v>
       </c>
@@ -1026,13 +1011,13 @@
         <v>81.43017578125</v>
       </c>
       <c r="G20">
-        <v>81.43017578125</v>
-      </c>
-      <c r="V20">
-        <v>11.7</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22">
+        <v>85.669921875</v>
+      </c>
+      <c r="H20">
+        <v>85.669921875</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" s="1">
         <v>47775950</v>
       </c>
@@ -1052,10 +1037,10 @@
         <v>49.449951171875</v>
       </c>
       <c r="G21">
-        <v>49.449951171875</v>
-      </c>
-      <c r="V21">
-        <v>22</v>
+        <v>87.72021484375</v>
+      </c>
+      <c r="H21">
+        <v>87.72021484375</v>
       </c>
     </row>
   </sheetData>

--- a/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao_20.xlsx
+++ b/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao_20.xlsx
@@ -593,6 +593,9 @@
       <c r="H2">
         <v>77.22021484375</v>
       </c>
+      <c r="V2">
+        <v>88.20999999999999</v>
+      </c>
     </row>
     <row r="3" spans="1:22">
       <c r="A3" s="1">
@@ -619,6 +622,9 @@
       <c r="H3">
         <v>77.6201171875</v>
       </c>
+      <c r="V3">
+        <v>79.01000000000001</v>
+      </c>
     </row>
     <row r="4" spans="1:22">
       <c r="A4" s="1">
@@ -645,6 +651,9 @@
       <c r="H4">
         <v>86.419921875</v>
       </c>
+      <c r="V4">
+        <v>47.39</v>
+      </c>
     </row>
     <row r="5" spans="1:22">
       <c r="A5" s="1">
@@ -659,6 +668,9 @@
       <c r="D5">
         <v>44.679931640625</v>
       </c>
+      <c r="V5">
+        <v>70.59999999999999</v>
+      </c>
     </row>
     <row r="6" spans="1:22">
       <c r="A6" s="1">
@@ -685,6 +697,9 @@
       <c r="H6">
         <v>93.02001953125</v>
       </c>
+      <c r="V6">
+        <v>83</v>
+      </c>
     </row>
     <row r="7" spans="1:22">
       <c r="A7" s="1">
@@ -711,6 +726,9 @@
       <c r="H7">
         <v>49.77001953125</v>
       </c>
+      <c r="V7">
+        <v>55.38</v>
+      </c>
     </row>
     <row r="8" spans="1:22">
       <c r="A8" s="1">
@@ -737,6 +755,9 @@
       <c r="H8">
         <v>63.8701171875</v>
       </c>
+      <c r="V8">
+        <v>64.81</v>
+      </c>
     </row>
     <row r="9" spans="1:22">
       <c r="A9" s="1">
@@ -763,6 +784,9 @@
       <c r="H9">
         <v>84.81982421875</v>
       </c>
+      <c r="V9">
+        <v>62.01</v>
+      </c>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" s="1">
@@ -789,6 +813,9 @@
       <c r="H10">
         <v>84.6201171875</v>
       </c>
+      <c r="V10">
+        <v>75.81</v>
+      </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="1">
@@ -806,6 +833,9 @@
       <c r="E11">
         <v>42.14990234375</v>
       </c>
+      <c r="V11">
+        <v>34.55</v>
+      </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1">
@@ -832,6 +862,9 @@
       <c r="H12">
         <v>93.06982421875</v>
       </c>
+      <c r="V12">
+        <v>75.36</v>
+      </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="1">
@@ -843,6 +876,9 @@
       <c r="C13">
         <v>0</v>
       </c>
+      <c r="V13">
+        <v>47.99</v>
+      </c>
     </row>
     <row r="14" spans="1:22">
       <c r="A14" s="1">
@@ -869,6 +905,9 @@
       <c r="H14">
         <v>72.759765625</v>
       </c>
+      <c r="V14">
+        <v>61.2</v>
+      </c>
     </row>
     <row r="15" spans="1:22">
       <c r="A15" s="1">
@@ -892,6 +931,9 @@
       <c r="G15">
         <v>41.169921875</v>
       </c>
+      <c r="V15">
+        <v>71.01000000000001</v>
+      </c>
     </row>
     <row r="16" spans="1:22">
       <c r="A16" s="1">
@@ -918,8 +960,11 @@
       <c r="H16">
         <v>88.240234375</v>
       </c>
-    </row>
-    <row r="17" spans="1:8">
+      <c r="V16">
+        <v>61.99</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22">
       <c r="A17" s="1">
         <v>19209079</v>
       </c>
@@ -944,8 +989,11 @@
       <c r="H17">
         <v>78.47021484375</v>
       </c>
-    </row>
-    <row r="18" spans="1:8">
+      <c r="V17">
+        <v>63.71</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22">
       <c r="A18" s="1">
         <v>19833277</v>
       </c>
@@ -970,8 +1018,11 @@
       <c r="H18">
         <v>87.919921875</v>
       </c>
-    </row>
-    <row r="19" spans="1:8">
+      <c r="V18">
+        <v>63.21</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22">
       <c r="A19" s="1">
         <v>20651178</v>
       </c>
@@ -990,8 +1041,11 @@
       <c r="F19">
         <v>42.56005859375</v>
       </c>
-    </row>
-    <row r="20" spans="1:8">
+      <c r="V19">
+        <v>67.59</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22">
       <c r="A20" s="1">
         <v>44810918</v>
       </c>
@@ -1016,8 +1070,11 @@
       <c r="H20">
         <v>85.669921875</v>
       </c>
-    </row>
-    <row r="21" spans="1:8">
+      <c r="V20">
+        <v>58.61</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22">
       <c r="A21" s="1">
         <v>47775950</v>
       </c>
@@ -1041,6 +1098,9 @@
       </c>
       <c r="H21">
         <v>87.72021484375</v>
+      </c>
+      <c r="V21">
+        <v>77.8</v>
       </c>
     </row>
   </sheetData>

--- a/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao_20.xlsx
+++ b/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao_20.xlsx
@@ -76,7 +76,7 @@
     <t>Rodada 19</t>
   </si>
   <si>
-    <t>Parcial Rodada 6</t>
+    <t>Parcial Rodada 7</t>
   </si>
   <si>
     <t>time_id</t>
@@ -591,10 +591,10 @@
         <v>77.22021484375</v>
       </c>
       <c r="H2">
-        <v>77.22021484375</v>
-      </c>
-      <c r="V2">
-        <v>88.20999999999999</v>
+        <v>88.2099609375</v>
+      </c>
+      <c r="I2">
+        <v>88.2099609375</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -620,10 +620,10 @@
         <v>77.6201171875</v>
       </c>
       <c r="H3">
-        <v>77.6201171875</v>
-      </c>
-      <c r="V3">
-        <v>79.01000000000001</v>
+        <v>79.009765625</v>
+      </c>
+      <c r="I3">
+        <v>79.009765625</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -649,10 +649,7 @@
         <v>86.419921875</v>
       </c>
       <c r="H4">
-        <v>86.419921875</v>
-      </c>
-      <c r="V4">
-        <v>47.39</v>
+        <v>47.389892578125</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -668,9 +665,6 @@
       <c r="D5">
         <v>44.679931640625</v>
       </c>
-      <c r="V5">
-        <v>70.59999999999999</v>
-      </c>
     </row>
     <row r="6" spans="1:22">
       <c r="A6" s="1">
@@ -695,9 +689,9 @@
         <v>93.02001953125</v>
       </c>
       <c r="H6">
-        <v>93.02001953125</v>
-      </c>
-      <c r="V6">
+        <v>83</v>
+      </c>
+      <c r="I6">
         <v>83</v>
       </c>
     </row>
@@ -724,10 +718,10 @@
         <v>49.77001953125</v>
       </c>
       <c r="H7">
-        <v>49.77001953125</v>
-      </c>
-      <c r="V7">
-        <v>55.38</v>
+        <v>55.3798828125</v>
+      </c>
+      <c r="I7">
+        <v>55.3798828125</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -753,10 +747,10 @@
         <v>63.8701171875</v>
       </c>
       <c r="H8">
-        <v>63.8701171875</v>
-      </c>
-      <c r="V8">
-        <v>64.81</v>
+        <v>64.81005859375</v>
+      </c>
+      <c r="I8">
+        <v>64.81005859375</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -782,10 +776,10 @@
         <v>84.81982421875</v>
       </c>
       <c r="H9">
-        <v>84.81982421875</v>
-      </c>
-      <c r="V9">
-        <v>62.01</v>
+        <v>62.010009765625</v>
+      </c>
+      <c r="I9">
+        <v>62.010009765625</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -811,10 +805,10 @@
         <v>84.6201171875</v>
       </c>
       <c r="H10">
-        <v>84.6201171875</v>
-      </c>
-      <c r="V10">
-        <v>75.81</v>
+        <v>75.81005859375</v>
+      </c>
+      <c r="I10">
+        <v>75.81005859375</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -833,9 +827,6 @@
       <c r="E11">
         <v>42.14990234375</v>
       </c>
-      <c r="V11">
-        <v>34.55</v>
-      </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1">
@@ -860,10 +851,10 @@
         <v>93.06982421875</v>
       </c>
       <c r="H12">
-        <v>93.06982421875</v>
-      </c>
-      <c r="V12">
-        <v>75.36</v>
+        <v>75.35986328125</v>
+      </c>
+      <c r="I12">
+        <v>75.35986328125</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -876,9 +867,6 @@
       <c r="C13">
         <v>0</v>
       </c>
-      <c r="V13">
-        <v>47.99</v>
-      </c>
     </row>
     <row r="14" spans="1:22">
       <c r="A14" s="1">
@@ -903,10 +891,10 @@
         <v>72.759765625</v>
       </c>
       <c r="H14">
-        <v>72.759765625</v>
-      </c>
-      <c r="V14">
-        <v>61.2</v>
+        <v>61.199951171875</v>
+      </c>
+      <c r="I14">
+        <v>61.199951171875</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -931,9 +919,6 @@
       <c r="G15">
         <v>41.169921875</v>
       </c>
-      <c r="V15">
-        <v>71.01000000000001</v>
-      </c>
     </row>
     <row r="16" spans="1:22">
       <c r="A16" s="1">
@@ -958,13 +943,13 @@
         <v>88.240234375</v>
       </c>
       <c r="H16">
-        <v>88.240234375</v>
-      </c>
-      <c r="V16">
-        <v>61.99</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22">
+        <v>61.989990234375</v>
+      </c>
+      <c r="I16">
+        <v>61.989990234375</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17" s="1">
         <v>19209079</v>
       </c>
@@ -987,13 +972,13 @@
         <v>78.47021484375</v>
       </c>
       <c r="H17">
-        <v>78.47021484375</v>
-      </c>
-      <c r="V17">
-        <v>63.71</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22">
+        <v>63.7099609375</v>
+      </c>
+      <c r="I17">
+        <v>63.7099609375</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18" s="1">
         <v>19833277</v>
       </c>
@@ -1016,13 +1001,13 @@
         <v>87.919921875</v>
       </c>
       <c r="H18">
-        <v>87.919921875</v>
-      </c>
-      <c r="V18">
-        <v>63.21</v>
-      </c>
-    </row>
-    <row r="19" spans="1:22">
+        <v>63.2099609375</v>
+      </c>
+      <c r="I18">
+        <v>63.2099609375</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
       <c r="A19" s="1">
         <v>20651178</v>
       </c>
@@ -1041,11 +1026,8 @@
       <c r="F19">
         <v>42.56005859375</v>
       </c>
-      <c r="V19">
-        <v>67.59</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22">
+    </row>
+    <row r="20" spans="1:9">
       <c r="A20" s="1">
         <v>44810918</v>
       </c>
@@ -1068,13 +1050,13 @@
         <v>85.669921875</v>
       </c>
       <c r="H20">
-        <v>85.669921875</v>
-      </c>
-      <c r="V20">
-        <v>58.61</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22">
+        <v>58.610107421875</v>
+      </c>
+      <c r="I20">
+        <v>58.610107421875</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
       <c r="A21" s="1">
         <v>47775950</v>
       </c>
@@ -1097,10 +1079,10 @@
         <v>87.72021484375</v>
       </c>
       <c r="H21">
-        <v>87.72021484375</v>
-      </c>
-      <c r="V21">
-        <v>77.8</v>
+        <v>77.7998046875</v>
+      </c>
+      <c r="I21">
+        <v>77.7998046875</v>
       </c>
     </row>
   </sheetData>

--- a/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao_20.xlsx
+++ b/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao_20.xlsx
@@ -596,6 +596,9 @@
       <c r="I2">
         <v>88.2099609375</v>
       </c>
+      <c r="V2">
+        <v>28.2</v>
+      </c>
     </row>
     <row r="3" spans="1:22">
       <c r="A3" s="1">
@@ -625,6 +628,9 @@
       <c r="I3">
         <v>79.009765625</v>
       </c>
+      <c r="V3">
+        <v>41.27</v>
+      </c>
     </row>
     <row r="4" spans="1:22">
       <c r="A4" s="1">
@@ -651,6 +657,9 @@
       <c r="H4">
         <v>47.389892578125</v>
       </c>
+      <c r="V4">
+        <v>38.87</v>
+      </c>
     </row>
     <row r="5" spans="1:22">
       <c r="A5" s="1">
@@ -665,6 +674,9 @@
       <c r="D5">
         <v>44.679931640625</v>
       </c>
+      <c r="V5">
+        <v>31.8</v>
+      </c>
     </row>
     <row r="6" spans="1:22">
       <c r="A6" s="1">
@@ -694,6 +706,9 @@
       <c r="I6">
         <v>83</v>
       </c>
+      <c r="V6">
+        <v>43.17</v>
+      </c>
     </row>
     <row r="7" spans="1:22">
       <c r="A7" s="1">
@@ -723,6 +738,9 @@
       <c r="I7">
         <v>55.3798828125</v>
       </c>
+      <c r="V7">
+        <v>12</v>
+      </c>
     </row>
     <row r="8" spans="1:22">
       <c r="A8" s="1">
@@ -752,6 +770,9 @@
       <c r="I8">
         <v>64.81005859375</v>
       </c>
+      <c r="V8">
+        <v>29.27</v>
+      </c>
     </row>
     <row r="9" spans="1:22">
       <c r="A9" s="1">
@@ -781,6 +802,9 @@
       <c r="I9">
         <v>62.010009765625</v>
       </c>
+      <c r="V9">
+        <v>30.77</v>
+      </c>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" s="1">
@@ -810,6 +834,9 @@
       <c r="I10">
         <v>75.81005859375</v>
       </c>
+      <c r="V10">
+        <v>48.67</v>
+      </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="1">
@@ -827,6 +854,9 @@
       <c r="E11">
         <v>42.14990234375</v>
       </c>
+      <c r="V11">
+        <v>49.5</v>
+      </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1">
@@ -856,6 +886,9 @@
       <c r="I12">
         <v>75.35986328125</v>
       </c>
+      <c r="V12">
+        <v>30.25</v>
+      </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="1">
@@ -867,6 +900,9 @@
       <c r="C13">
         <v>0</v>
       </c>
+      <c r="V13">
+        <v>24.05</v>
+      </c>
     </row>
     <row r="14" spans="1:22">
       <c r="A14" s="1">
@@ -896,6 +932,9 @@
       <c r="I14">
         <v>61.199951171875</v>
       </c>
+      <c r="V14">
+        <v>44.15</v>
+      </c>
     </row>
     <row r="15" spans="1:22">
       <c r="A15" s="1">
@@ -919,6 +958,9 @@
       <c r="G15">
         <v>41.169921875</v>
       </c>
+      <c r="V15">
+        <v>40.27</v>
+      </c>
     </row>
     <row r="16" spans="1:22">
       <c r="A16" s="1">
@@ -948,8 +990,11 @@
       <c r="I16">
         <v>61.989990234375</v>
       </c>
-    </row>
-    <row r="17" spans="1:9">
+      <c r="V16">
+        <v>28.9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22">
       <c r="A17" s="1">
         <v>19209079</v>
       </c>
@@ -977,8 +1022,11 @@
       <c r="I17">
         <v>63.7099609375</v>
       </c>
-    </row>
-    <row r="18" spans="1:9">
+      <c r="V17">
+        <v>35.7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22">
       <c r="A18" s="1">
         <v>19833277</v>
       </c>
@@ -1006,8 +1054,11 @@
       <c r="I18">
         <v>63.2099609375</v>
       </c>
-    </row>
-    <row r="19" spans="1:9">
+      <c r="V18">
+        <v>49.97</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22">
       <c r="A19" s="1">
         <v>20651178</v>
       </c>
@@ -1026,8 +1077,11 @@
       <c r="F19">
         <v>42.56005859375</v>
       </c>
-    </row>
-    <row r="20" spans="1:9">
+      <c r="V19">
+        <v>32.97</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22">
       <c r="A20" s="1">
         <v>44810918</v>
       </c>
@@ -1055,8 +1109,11 @@
       <c r="I20">
         <v>58.610107421875</v>
       </c>
-    </row>
-    <row r="21" spans="1:9">
+      <c r="V20">
+        <v>45.37</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22">
       <c r="A21" s="1">
         <v>47775950</v>
       </c>
@@ -1083,6 +1140,9 @@
       </c>
       <c r="I21">
         <v>77.7998046875</v>
+      </c>
+      <c r="V21">
+        <v>35.34</v>
       </c>
     </row>
   </sheetData>

--- a/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao_20.xlsx
+++ b/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao_20.xlsx
@@ -76,7 +76,7 @@
     <t>Rodada 19</t>
   </si>
   <si>
-    <t>Parcial Rodada 7</t>
+    <t>Parcial Rodada 8</t>
   </si>
   <si>
     <t>time_id</t>
@@ -594,10 +594,10 @@
         <v>88.2099609375</v>
       </c>
       <c r="I2">
-        <v>88.2099609375</v>
-      </c>
-      <c r="V2">
-        <v>28.2</v>
+        <v>61.110107421875</v>
+      </c>
+      <c r="J2">
+        <v>61.110107421875</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -626,10 +626,10 @@
         <v>79.009765625</v>
       </c>
       <c r="I3">
-        <v>79.009765625</v>
-      </c>
-      <c r="V3">
-        <v>41.27</v>
+        <v>65.47021484375</v>
+      </c>
+      <c r="J3">
+        <v>65.47021484375</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -657,9 +657,6 @@
       <c r="H4">
         <v>47.389892578125</v>
       </c>
-      <c r="V4">
-        <v>38.87</v>
-      </c>
     </row>
     <row r="5" spans="1:22">
       <c r="A5" s="1">
@@ -674,9 +671,6 @@
       <c r="D5">
         <v>44.679931640625</v>
       </c>
-      <c r="V5">
-        <v>31.8</v>
-      </c>
     </row>
     <row r="6" spans="1:22">
       <c r="A6" s="1">
@@ -704,10 +698,10 @@
         <v>83</v>
       </c>
       <c r="I6">
-        <v>83</v>
-      </c>
-      <c r="V6">
-        <v>43.17</v>
+        <v>76.97021484375</v>
+      </c>
+      <c r="J6">
+        <v>76.97021484375</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -736,10 +730,10 @@
         <v>55.3798828125</v>
       </c>
       <c r="I7">
-        <v>55.3798828125</v>
-      </c>
-      <c r="V7">
-        <v>12</v>
+        <v>61.8701171875</v>
+      </c>
+      <c r="J7">
+        <v>61.8701171875</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -768,10 +762,10 @@
         <v>64.81005859375</v>
       </c>
       <c r="I8">
-        <v>64.81005859375</v>
-      </c>
-      <c r="V8">
-        <v>29.27</v>
+        <v>55.52001953125</v>
+      </c>
+      <c r="J8">
+        <v>55.52001953125</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -800,10 +794,10 @@
         <v>62.010009765625</v>
       </c>
       <c r="I9">
-        <v>62.010009765625</v>
-      </c>
-      <c r="V9">
-        <v>30.77</v>
+        <v>77.06982421875</v>
+      </c>
+      <c r="J9">
+        <v>77.06982421875</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -832,10 +826,10 @@
         <v>75.81005859375</v>
       </c>
       <c r="I10">
-        <v>75.81005859375</v>
-      </c>
-      <c r="V10">
-        <v>48.67</v>
+        <v>83.22021484375</v>
+      </c>
+      <c r="J10">
+        <v>83.22021484375</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -854,9 +848,6 @@
       <c r="E11">
         <v>42.14990234375</v>
       </c>
-      <c r="V11">
-        <v>49.5</v>
-      </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1">
@@ -884,10 +875,10 @@
         <v>75.35986328125</v>
       </c>
       <c r="I12">
-        <v>75.35986328125</v>
-      </c>
-      <c r="V12">
-        <v>30.25</v>
+        <v>100.25</v>
+      </c>
+      <c r="J12">
+        <v>100.25</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -900,9 +891,6 @@
       <c r="C13">
         <v>0</v>
       </c>
-      <c r="V13">
-        <v>24.05</v>
-      </c>
     </row>
     <row r="14" spans="1:22">
       <c r="A14" s="1">
@@ -930,10 +918,10 @@
         <v>61.199951171875</v>
       </c>
       <c r="I14">
-        <v>61.199951171875</v>
-      </c>
-      <c r="V14">
-        <v>44.15</v>
+        <v>69.60009765625</v>
+      </c>
+      <c r="J14">
+        <v>69.60009765625</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -958,9 +946,6 @@
       <c r="G15">
         <v>41.169921875</v>
       </c>
-      <c r="V15">
-        <v>40.27</v>
-      </c>
     </row>
     <row r="16" spans="1:22">
       <c r="A16" s="1">
@@ -988,13 +973,10 @@
         <v>61.989990234375</v>
       </c>
       <c r="I16">
-        <v>61.989990234375</v>
-      </c>
-      <c r="V16">
-        <v>28.9</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22">
+        <v>48.469970703125</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
       <c r="A17" s="1">
         <v>19209079</v>
       </c>
@@ -1020,13 +1002,13 @@
         <v>63.7099609375</v>
       </c>
       <c r="I17">
-        <v>63.7099609375</v>
-      </c>
-      <c r="V17">
-        <v>35.7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22">
+        <v>99.85986328125</v>
+      </c>
+      <c r="J17">
+        <v>99.85986328125</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18" s="1">
         <v>19833277</v>
       </c>
@@ -1052,13 +1034,13 @@
         <v>63.2099609375</v>
       </c>
       <c r="I18">
-        <v>63.2099609375</v>
-      </c>
-      <c r="V18">
-        <v>49.97</v>
-      </c>
-    </row>
-    <row r="19" spans="1:22">
+        <v>70.81982421875</v>
+      </c>
+      <c r="J18">
+        <v>70.81982421875</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19" s="1">
         <v>20651178</v>
       </c>
@@ -1077,11 +1059,8 @@
       <c r="F19">
         <v>42.56005859375</v>
       </c>
-      <c r="V19">
-        <v>32.97</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22">
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20" s="1">
         <v>44810918</v>
       </c>
@@ -1107,13 +1086,13 @@
         <v>58.610107421875</v>
       </c>
       <c r="I20">
-        <v>58.610107421875</v>
-      </c>
-      <c r="V20">
-        <v>45.37</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22">
+        <v>81.56982421875</v>
+      </c>
+      <c r="J20">
+        <v>81.56982421875</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" s="1">
         <v>47775950</v>
       </c>
@@ -1139,10 +1118,10 @@
         <v>77.7998046875</v>
       </c>
       <c r="I21">
-        <v>77.7998046875</v>
-      </c>
-      <c r="V21">
-        <v>35.34</v>
+        <v>57.93994140625</v>
+      </c>
+      <c r="J21">
+        <v>57.93994140625</v>
       </c>
     </row>
   </sheetData>

--- a/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao_20.xlsx
+++ b/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao_20.xlsx
@@ -76,7 +76,7 @@
     <t>Rodada 19</t>
   </si>
   <si>
-    <t>Parcial Rodada 8</t>
+    <t>Parcial Rodada 9</t>
   </si>
   <si>
     <t>time_id</t>
@@ -597,7 +597,10 @@
         <v>61.110107421875</v>
       </c>
       <c r="J2">
-        <v>61.110107421875</v>
+        <v>82.81982421875</v>
+      </c>
+      <c r="K2">
+        <v>82.81982421875</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -629,7 +632,10 @@
         <v>65.47021484375</v>
       </c>
       <c r="J3">
-        <v>65.47021484375</v>
+        <v>80.85009765625</v>
+      </c>
+      <c r="K3">
+        <v>80.85009765625</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -701,7 +707,10 @@
         <v>76.97021484375</v>
       </c>
       <c r="J6">
-        <v>76.97021484375</v>
+        <v>76.4501953125</v>
+      </c>
+      <c r="K6">
+        <v>76.4501953125</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -733,7 +742,10 @@
         <v>61.8701171875</v>
       </c>
       <c r="J7">
-        <v>61.8701171875</v>
+        <v>70.5400390625</v>
+      </c>
+      <c r="K7">
+        <v>70.5400390625</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -765,7 +777,10 @@
         <v>55.52001953125</v>
       </c>
       <c r="J8">
-        <v>55.52001953125</v>
+        <v>71.75</v>
+      </c>
+      <c r="K8">
+        <v>71.75</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -797,7 +812,10 @@
         <v>77.06982421875</v>
       </c>
       <c r="J9">
-        <v>77.06982421875</v>
+        <v>80.0498046875</v>
+      </c>
+      <c r="K9">
+        <v>80.0498046875</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -829,7 +847,10 @@
         <v>83.22021484375</v>
       </c>
       <c r="J10">
-        <v>83.22021484375</v>
+        <v>85.64990234375</v>
+      </c>
+      <c r="K10">
+        <v>85.64990234375</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -878,7 +899,10 @@
         <v>100.25</v>
       </c>
       <c r="J12">
-        <v>100.25</v>
+        <v>75.52001953125</v>
+      </c>
+      <c r="K12">
+        <v>75.52001953125</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -921,7 +945,10 @@
         <v>69.60009765625</v>
       </c>
       <c r="J14">
-        <v>69.60009765625</v>
+        <v>67.14990234375</v>
+      </c>
+      <c r="K14">
+        <v>67.14990234375</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -976,7 +1003,7 @@
         <v>48.469970703125</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:11">
       <c r="A17" s="1">
         <v>19209079</v>
       </c>
@@ -1005,10 +1032,13 @@
         <v>99.85986328125</v>
       </c>
       <c r="J17">
-        <v>99.85986328125</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
+        <v>58.679931640625</v>
+      </c>
+      <c r="K17">
+        <v>58.679931640625</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
       <c r="A18" s="1">
         <v>19833277</v>
       </c>
@@ -1037,10 +1067,13 @@
         <v>70.81982421875</v>
       </c>
       <c r="J18">
-        <v>70.81982421875</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
+        <v>77.5498046875</v>
+      </c>
+      <c r="K18">
+        <v>77.5498046875</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
       <c r="A19" s="1">
         <v>20651178</v>
       </c>
@@ -1060,7 +1093,7 @@
         <v>42.56005859375</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:11">
       <c r="A20" s="1">
         <v>44810918</v>
       </c>
@@ -1089,10 +1122,13 @@
         <v>81.56982421875</v>
       </c>
       <c r="J20">
-        <v>81.56982421875</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
+        <v>73.35009765625</v>
+      </c>
+      <c r="K20">
+        <v>73.35009765625</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
       <c r="A21" s="1">
         <v>47775950</v>
       </c>
@@ -1121,7 +1157,7 @@
         <v>57.93994140625</v>
       </c>
       <c r="J21">
-        <v>57.93994140625</v>
+        <v>42.89990234375</v>
       </c>
     </row>
   </sheetData>

--- a/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao_20.xlsx
+++ b/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao_20.xlsx
@@ -602,6 +602,9 @@
       <c r="K2">
         <v>82.81982421875</v>
       </c>
+      <c r="V2">
+        <v>87.73999999999999</v>
+      </c>
     </row>
     <row r="3" spans="1:22">
       <c r="A3" s="1">
@@ -637,6 +640,9 @@
       <c r="K3">
         <v>80.85009765625</v>
       </c>
+      <c r="V3">
+        <v>94.58</v>
+      </c>
     </row>
     <row r="4" spans="1:22">
       <c r="A4" s="1">
@@ -663,6 +669,9 @@
       <c r="H4">
         <v>47.389892578125</v>
       </c>
+      <c r="V4">
+        <v>85.95999999999999</v>
+      </c>
     </row>
     <row r="5" spans="1:22">
       <c r="A5" s="1">
@@ -677,6 +686,9 @@
       <c r="D5">
         <v>44.679931640625</v>
       </c>
+      <c r="V5">
+        <v>96.45999999999999</v>
+      </c>
     </row>
     <row r="6" spans="1:22">
       <c r="A6" s="1">
@@ -712,6 +724,9 @@
       <c r="K6">
         <v>76.4501953125</v>
       </c>
+      <c r="V6">
+        <v>86.34999999999999</v>
+      </c>
     </row>
     <row r="7" spans="1:22">
       <c r="A7" s="1">
@@ -747,6 +762,9 @@
       <c r="K7">
         <v>70.5400390625</v>
       </c>
+      <c r="V7">
+        <v>39.7</v>
+      </c>
     </row>
     <row r="8" spans="1:22">
       <c r="A8" s="1">
@@ -782,6 +800,9 @@
       <c r="K8">
         <v>71.75</v>
       </c>
+      <c r="V8">
+        <v>49.76</v>
+      </c>
     </row>
     <row r="9" spans="1:22">
       <c r="A9" s="1">
@@ -817,6 +838,9 @@
       <c r="K9">
         <v>80.0498046875</v>
       </c>
+      <c r="V9">
+        <v>61.01</v>
+      </c>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" s="1">
@@ -852,6 +876,9 @@
       <c r="K10">
         <v>85.64990234375</v>
       </c>
+      <c r="V10">
+        <v>68.44</v>
+      </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="1">
@@ -869,6 +896,9 @@
       <c r="E11">
         <v>42.14990234375</v>
       </c>
+      <c r="V11">
+        <v>68.98</v>
+      </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1">
@@ -904,6 +934,9 @@
       <c r="K12">
         <v>75.52001953125</v>
       </c>
+      <c r="V12">
+        <v>68.90000000000001</v>
+      </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="1">
@@ -915,6 +948,9 @@
       <c r="C13">
         <v>0</v>
       </c>
+      <c r="V13">
+        <v>70.48</v>
+      </c>
     </row>
     <row r="14" spans="1:22">
       <c r="A14" s="1">
@@ -950,6 +986,9 @@
       <c r="K14">
         <v>67.14990234375</v>
       </c>
+      <c r="V14">
+        <v>61.6</v>
+      </c>
     </row>
     <row r="15" spans="1:22">
       <c r="A15" s="1">
@@ -973,6 +1012,9 @@
       <c r="G15">
         <v>41.169921875</v>
       </c>
+      <c r="V15">
+        <v>71.04000000000001</v>
+      </c>
     </row>
     <row r="16" spans="1:22">
       <c r="A16" s="1">
@@ -1002,8 +1044,11 @@
       <c r="I16">
         <v>48.469970703125</v>
       </c>
-    </row>
-    <row r="17" spans="1:11">
+      <c r="V16">
+        <v>85.53</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22">
       <c r="A17" s="1">
         <v>19209079</v>
       </c>
@@ -1037,8 +1082,11 @@
       <c r="K17">
         <v>58.679931640625</v>
       </c>
-    </row>
-    <row r="18" spans="1:11">
+      <c r="V17">
+        <v>88.64</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22">
       <c r="A18" s="1">
         <v>19833277</v>
       </c>
@@ -1072,8 +1120,11 @@
       <c r="K18">
         <v>77.5498046875</v>
       </c>
-    </row>
-    <row r="19" spans="1:11">
+      <c r="V18">
+        <v>73.98</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22">
       <c r="A19" s="1">
         <v>20651178</v>
       </c>
@@ -1092,8 +1143,11 @@
       <c r="F19">
         <v>42.56005859375</v>
       </c>
-    </row>
-    <row r="20" spans="1:11">
+      <c r="V19">
+        <v>80.34</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22">
       <c r="A20" s="1">
         <v>44810918</v>
       </c>
@@ -1127,8 +1181,11 @@
       <c r="K20">
         <v>73.35009765625</v>
       </c>
-    </row>
-    <row r="21" spans="1:11">
+      <c r="V20">
+        <v>104.68</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22">
       <c r="A21" s="1">
         <v>47775950</v>
       </c>
@@ -1158,6 +1215,9 @@
       </c>
       <c r="J21">
         <v>42.89990234375</v>
+      </c>
+      <c r="V21">
+        <v>97.68000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao_20.xlsx
+++ b/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao_20.xlsx
@@ -76,7 +76,7 @@
     <t>Rodada 19</t>
   </si>
   <si>
-    <t>Parcial Rodada 9</t>
+    <t>Parcial Rodada 10</t>
   </si>
   <si>
     <t>time_id</t>
@@ -600,10 +600,10 @@
         <v>82.81982421875</v>
       </c>
       <c r="K2">
-        <v>82.81982421875</v>
-      </c>
-      <c r="V2">
-        <v>87.73999999999999</v>
+        <v>85.93994140625</v>
+      </c>
+      <c r="L2">
+        <v>85.93994140625</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -638,10 +638,10 @@
         <v>80.85009765625</v>
       </c>
       <c r="K3">
-        <v>80.85009765625</v>
-      </c>
-      <c r="V3">
-        <v>94.58</v>
+        <v>94.27978515625</v>
+      </c>
+      <c r="L3">
+        <v>94.27978515625</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -669,9 +669,6 @@
       <c r="H4">
         <v>47.389892578125</v>
       </c>
-      <c r="V4">
-        <v>85.95999999999999</v>
-      </c>
     </row>
     <row r="5" spans="1:22">
       <c r="A5" s="1">
@@ -686,9 +683,6 @@
       <c r="D5">
         <v>44.679931640625</v>
       </c>
-      <c r="V5">
-        <v>96.45999999999999</v>
-      </c>
     </row>
     <row r="6" spans="1:22">
       <c r="A6" s="1">
@@ -722,10 +716,10 @@
         <v>76.4501953125</v>
       </c>
       <c r="K6">
-        <v>76.4501953125</v>
-      </c>
-      <c r="V6">
-        <v>86.34999999999999</v>
+        <v>85.85009765625</v>
+      </c>
+      <c r="L6">
+        <v>85.85009765625</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -760,10 +754,7 @@
         <v>70.5400390625</v>
       </c>
       <c r="K7">
-        <v>70.5400390625</v>
-      </c>
-      <c r="V7">
-        <v>39.7</v>
+        <v>39.699951171875</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -798,10 +789,10 @@
         <v>71.75</v>
       </c>
       <c r="K8">
-        <v>71.75</v>
-      </c>
-      <c r="V8">
-        <v>49.76</v>
+        <v>49.760009765625</v>
+      </c>
+      <c r="L8">
+        <v>49.760009765625</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -836,10 +827,10 @@
         <v>80.0498046875</v>
       </c>
       <c r="K9">
-        <v>80.0498046875</v>
-      </c>
-      <c r="V9">
-        <v>61.01</v>
+        <v>59.010009765625</v>
+      </c>
+      <c r="L9">
+        <v>59.010009765625</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -874,10 +865,10 @@
         <v>85.64990234375</v>
       </c>
       <c r="K10">
-        <v>85.64990234375</v>
-      </c>
-      <c r="V10">
-        <v>68.44</v>
+        <v>66.93994140625</v>
+      </c>
+      <c r="L10">
+        <v>66.93994140625</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -896,9 +887,6 @@
       <c r="E11">
         <v>42.14990234375</v>
       </c>
-      <c r="V11">
-        <v>68.98</v>
-      </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1">
@@ -932,10 +920,10 @@
         <v>75.52001953125</v>
       </c>
       <c r="K12">
-        <v>75.52001953125</v>
-      </c>
-      <c r="V12">
-        <v>68.90000000000001</v>
+        <v>70.10009765625</v>
+      </c>
+      <c r="L12">
+        <v>70.10009765625</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -948,9 +936,6 @@
       <c r="C13">
         <v>0</v>
       </c>
-      <c r="V13">
-        <v>70.48</v>
-      </c>
     </row>
     <row r="14" spans="1:22">
       <c r="A14" s="1">
@@ -984,10 +969,10 @@
         <v>67.14990234375</v>
       </c>
       <c r="K14">
-        <v>67.14990234375</v>
-      </c>
-      <c r="V14">
-        <v>61.6</v>
+        <v>62.89990234375</v>
+      </c>
+      <c r="L14">
+        <v>62.89990234375</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -1012,9 +997,6 @@
       <c r="G15">
         <v>41.169921875</v>
       </c>
-      <c r="V15">
-        <v>71.04000000000001</v>
-      </c>
     </row>
     <row r="16" spans="1:22">
       <c r="A16" s="1">
@@ -1044,11 +1026,8 @@
       <c r="I16">
         <v>48.469970703125</v>
       </c>
-      <c r="V16">
-        <v>85.53</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22">
+    </row>
+    <row r="17" spans="1:12">
       <c r="A17" s="1">
         <v>19209079</v>
       </c>
@@ -1080,13 +1059,13 @@
         <v>58.679931640625</v>
       </c>
       <c r="K17">
-        <v>58.679931640625</v>
-      </c>
-      <c r="V17">
-        <v>88.64</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22">
+        <v>87.14013671875</v>
+      </c>
+      <c r="L17">
+        <v>87.14013671875</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
       <c r="A18" s="1">
         <v>19833277</v>
       </c>
@@ -1118,13 +1097,13 @@
         <v>77.5498046875</v>
       </c>
       <c r="K18">
-        <v>77.5498046875</v>
-      </c>
-      <c r="V18">
-        <v>73.98</v>
-      </c>
-    </row>
-    <row r="19" spans="1:22">
+        <v>73.68017578125</v>
+      </c>
+      <c r="L18">
+        <v>73.68017578125</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
       <c r="A19" s="1">
         <v>20651178</v>
       </c>
@@ -1143,11 +1122,8 @@
       <c r="F19">
         <v>42.56005859375</v>
       </c>
-      <c r="V19">
-        <v>80.34</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22">
+    </row>
+    <row r="20" spans="1:12">
       <c r="A20" s="1">
         <v>44810918</v>
       </c>
@@ -1179,13 +1155,13 @@
         <v>73.35009765625</v>
       </c>
       <c r="K20">
-        <v>73.35009765625</v>
-      </c>
-      <c r="V20">
-        <v>104.68</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22">
+        <v>104.68017578125</v>
+      </c>
+      <c r="L20">
+        <v>104.68017578125</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
       <c r="A21" s="1">
         <v>47775950</v>
       </c>
@@ -1215,9 +1191,6 @@
       </c>
       <c r="J21">
         <v>42.89990234375</v>
-      </c>
-      <c r="V21">
-        <v>97.68000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao_20.xlsx
+++ b/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao_20.xlsx
@@ -605,6 +605,9 @@
       <c r="L2">
         <v>85.93994140625</v>
       </c>
+      <c r="V2">
+        <v>43.59</v>
+      </c>
     </row>
     <row r="3" spans="1:22">
       <c r="A3" s="1">
@@ -643,6 +646,9 @@
       <c r="L3">
         <v>94.27978515625</v>
       </c>
+      <c r="V3">
+        <v>71.17</v>
+      </c>
     </row>
     <row r="4" spans="1:22">
       <c r="A4" s="1">
@@ -669,6 +675,9 @@
       <c r="H4">
         <v>47.389892578125</v>
       </c>
+      <c r="V4">
+        <v>39.87</v>
+      </c>
     </row>
     <row r="5" spans="1:22">
       <c r="A5" s="1">
@@ -683,6 +692,9 @@
       <c r="D5">
         <v>44.679931640625</v>
       </c>
+      <c r="V5">
+        <v>69.06999999999999</v>
+      </c>
     </row>
     <row r="6" spans="1:22">
       <c r="A6" s="1">
@@ -721,6 +733,9 @@
       <c r="L6">
         <v>85.85009765625</v>
       </c>
+      <c r="V6">
+        <v>59.29</v>
+      </c>
     </row>
     <row r="7" spans="1:22">
       <c r="A7" s="1">
@@ -756,6 +771,9 @@
       <c r="K7">
         <v>39.699951171875</v>
       </c>
+      <c r="V7">
+        <v>32.15</v>
+      </c>
     </row>
     <row r="8" spans="1:22">
       <c r="A8" s="1">
@@ -794,6 +812,9 @@
       <c r="L8">
         <v>49.760009765625</v>
       </c>
+      <c r="V8">
+        <v>39.58</v>
+      </c>
     </row>
     <row r="9" spans="1:22">
       <c r="A9" s="1">
@@ -832,6 +853,9 @@
       <c r="L9">
         <v>59.010009765625</v>
       </c>
+      <c r="V9">
+        <v>60.57</v>
+      </c>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" s="1">
@@ -870,6 +894,9 @@
       <c r="L10">
         <v>66.93994140625</v>
       </c>
+      <c r="V10">
+        <v>59.75</v>
+      </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="1">
@@ -887,6 +914,9 @@
       <c r="E11">
         <v>42.14990234375</v>
       </c>
+      <c r="V11">
+        <v>19.4</v>
+      </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1">
@@ -925,6 +955,9 @@
       <c r="L12">
         <v>70.10009765625</v>
       </c>
+      <c r="V12">
+        <v>42.89</v>
+      </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="1">
@@ -936,6 +969,9 @@
       <c r="C13">
         <v>0</v>
       </c>
+      <c r="V13">
+        <v>67.78</v>
+      </c>
     </row>
     <row r="14" spans="1:22">
       <c r="A14" s="1">
@@ -974,6 +1010,9 @@
       <c r="L14">
         <v>62.89990234375</v>
       </c>
+      <c r="V14">
+        <v>44.05</v>
+      </c>
     </row>
     <row r="15" spans="1:22">
       <c r="A15" s="1">
@@ -997,6 +1036,9 @@
       <c r="G15">
         <v>41.169921875</v>
       </c>
+      <c r="V15">
+        <v>54.48</v>
+      </c>
     </row>
     <row r="16" spans="1:22">
       <c r="A16" s="1">
@@ -1026,8 +1068,11 @@
       <c r="I16">
         <v>48.469970703125</v>
       </c>
-    </row>
-    <row r="17" spans="1:12">
+      <c r="V16">
+        <v>55.58</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22">
       <c r="A17" s="1">
         <v>19209079</v>
       </c>
@@ -1064,8 +1109,11 @@
       <c r="L17">
         <v>87.14013671875</v>
       </c>
-    </row>
-    <row r="18" spans="1:12">
+      <c r="V17">
+        <v>56.47</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22">
       <c r="A18" s="1">
         <v>19833277</v>
       </c>
@@ -1102,8 +1150,11 @@
       <c r="L18">
         <v>73.68017578125</v>
       </c>
-    </row>
-    <row r="19" spans="1:12">
+      <c r="V18">
+        <v>31.57</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22">
       <c r="A19" s="1">
         <v>20651178</v>
       </c>
@@ -1122,8 +1173,11 @@
       <c r="F19">
         <v>42.56005859375</v>
       </c>
-    </row>
-    <row r="20" spans="1:12">
+      <c r="V19">
+        <v>60.45</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22">
       <c r="A20" s="1">
         <v>44810918</v>
       </c>
@@ -1160,8 +1214,11 @@
       <c r="L20">
         <v>104.68017578125</v>
       </c>
-    </row>
-    <row r="21" spans="1:12">
+      <c r="V20">
+        <v>67.29000000000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22">
       <c r="A21" s="1">
         <v>47775950</v>
       </c>
@@ -1191,6 +1248,9 @@
       </c>
       <c r="J21">
         <v>42.89990234375</v>
+      </c>
+      <c r="V21">
+        <v>66.56999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao_20.xlsx
+++ b/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao_20.xlsx
@@ -76,7 +76,7 @@
     <t>Rodada 19</t>
   </si>
   <si>
-    <t>Parcial Rodada 10</t>
+    <t>Parcial Rodada 11</t>
   </si>
   <si>
     <t>time_id</t>
@@ -603,10 +603,10 @@
         <v>85.93994140625</v>
       </c>
       <c r="L2">
-        <v>85.93994140625</v>
-      </c>
-      <c r="V2">
-        <v>43.59</v>
+        <v>43.590087890625</v>
+      </c>
+      <c r="M2">
+        <v>43.590087890625</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -644,10 +644,10 @@
         <v>94.27978515625</v>
       </c>
       <c r="L3">
-        <v>94.27978515625</v>
-      </c>
-      <c r="V3">
-        <v>71.17</v>
+        <v>70.77001953125</v>
+      </c>
+      <c r="M3">
+        <v>70.77001953125</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -675,9 +675,6 @@
       <c r="H4">
         <v>47.389892578125</v>
       </c>
-      <c r="V4">
-        <v>39.87</v>
-      </c>
     </row>
     <row r="5" spans="1:22">
       <c r="A5" s="1">
@@ -692,9 +689,6 @@
       <c r="D5">
         <v>44.679931640625</v>
       </c>
-      <c r="V5">
-        <v>69.06999999999999</v>
-      </c>
     </row>
     <row r="6" spans="1:22">
       <c r="A6" s="1">
@@ -731,10 +725,10 @@
         <v>85.85009765625</v>
       </c>
       <c r="L6">
-        <v>85.85009765625</v>
-      </c>
-      <c r="V6">
-        <v>59.29</v>
+        <v>58.090087890625</v>
+      </c>
+      <c r="M6">
+        <v>58.090087890625</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -771,9 +765,6 @@
       <c r="K7">
         <v>39.699951171875</v>
       </c>
-      <c r="V7">
-        <v>32.15</v>
-      </c>
     </row>
     <row r="8" spans="1:22">
       <c r="A8" s="1">
@@ -810,10 +801,7 @@
         <v>49.760009765625</v>
       </c>
       <c r="L8">
-        <v>49.760009765625</v>
-      </c>
-      <c r="V8">
-        <v>39.58</v>
+        <v>38.780029296875</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -851,10 +839,10 @@
         <v>59.010009765625</v>
       </c>
       <c r="L9">
-        <v>59.010009765625</v>
-      </c>
-      <c r="V9">
-        <v>60.57</v>
+        <v>60.169921875</v>
+      </c>
+      <c r="M9">
+        <v>60.169921875</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -892,10 +880,10 @@
         <v>66.93994140625</v>
       </c>
       <c r="L10">
-        <v>66.93994140625</v>
-      </c>
-      <c r="V10">
-        <v>59.75</v>
+        <v>58.949951171875</v>
+      </c>
+      <c r="M10">
+        <v>58.949951171875</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -914,9 +902,6 @@
       <c r="E11">
         <v>42.14990234375</v>
       </c>
-      <c r="V11">
-        <v>19.4</v>
-      </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1">
@@ -953,10 +938,10 @@
         <v>70.10009765625</v>
       </c>
       <c r="L12">
-        <v>70.10009765625</v>
-      </c>
-      <c r="V12">
-        <v>42.89</v>
+        <v>42.090087890625</v>
+      </c>
+      <c r="M12">
+        <v>42.090087890625</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -969,9 +954,6 @@
       <c r="C13">
         <v>0</v>
       </c>
-      <c r="V13">
-        <v>67.78</v>
-      </c>
     </row>
     <row r="14" spans="1:22">
       <c r="A14" s="1">
@@ -1008,10 +990,10 @@
         <v>62.89990234375</v>
       </c>
       <c r="L14">
-        <v>62.89990234375</v>
-      </c>
-      <c r="V14">
-        <v>44.05</v>
+        <v>43.25</v>
+      </c>
+      <c r="M14">
+        <v>43.25</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -1036,9 +1018,6 @@
       <c r="G15">
         <v>41.169921875</v>
       </c>
-      <c r="V15">
-        <v>54.48</v>
-      </c>
     </row>
     <row r="16" spans="1:22">
       <c r="A16" s="1">
@@ -1068,11 +1047,8 @@
       <c r="I16">
         <v>48.469970703125</v>
       </c>
-      <c r="V16">
-        <v>55.58</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22">
+    </row>
+    <row r="17" spans="1:13">
       <c r="A17" s="1">
         <v>19209079</v>
       </c>
@@ -1107,13 +1083,13 @@
         <v>87.14013671875</v>
       </c>
       <c r="L17">
-        <v>87.14013671875</v>
-      </c>
-      <c r="V17">
-        <v>56.47</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22">
+        <v>55.27001953125</v>
+      </c>
+      <c r="M17">
+        <v>55.27001953125</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
       <c r="A18" s="1">
         <v>19833277</v>
       </c>
@@ -1148,13 +1124,10 @@
         <v>73.68017578125</v>
       </c>
       <c r="L18">
-        <v>73.68017578125</v>
-      </c>
-      <c r="V18">
-        <v>31.57</v>
-      </c>
-    </row>
-    <row r="19" spans="1:22">
+        <v>30.3699951171875</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
       <c r="A19" s="1">
         <v>20651178</v>
       </c>
@@ -1173,11 +1146,8 @@
       <c r="F19">
         <v>42.56005859375</v>
       </c>
-      <c r="V19">
-        <v>60.45</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22">
+    </row>
+    <row r="20" spans="1:13">
       <c r="A20" s="1">
         <v>44810918</v>
       </c>
@@ -1212,13 +1182,13 @@
         <v>104.68017578125</v>
       </c>
       <c r="L20">
-        <v>104.68017578125</v>
-      </c>
-      <c r="V20">
-        <v>67.29000000000001</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22">
+        <v>66.89013671875</v>
+      </c>
+      <c r="M20">
+        <v>66.89013671875</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
       <c r="A21" s="1">
         <v>47775950</v>
       </c>
@@ -1248,9 +1218,6 @@
       </c>
       <c r="J21">
         <v>42.89990234375</v>
-      </c>
-      <c r="V21">
-        <v>66.56999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao_20.xlsx
+++ b/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao_20.xlsx
@@ -76,7 +76,7 @@
     <t>Rodada 19</t>
   </si>
   <si>
-    <t>Parcial Rodada 11</t>
+    <t>Parcial Rodada 10</t>
   </si>
   <si>
     <t>time_id</t>
@@ -603,10 +603,10 @@
         <v>85.93994140625</v>
       </c>
       <c r="L2">
-        <v>43.590087890625</v>
-      </c>
-      <c r="M2">
-        <v>43.590087890625</v>
+        <v>85.93994140625</v>
+      </c>
+      <c r="V2">
+        <v>43.59</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -644,10 +644,10 @@
         <v>94.27978515625</v>
       </c>
       <c r="L3">
-        <v>70.77001953125</v>
-      </c>
-      <c r="M3">
-        <v>70.77001953125</v>
+        <v>94.27978515625</v>
+      </c>
+      <c r="V3">
+        <v>71.17</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -675,6 +675,9 @@
       <c r="H4">
         <v>47.389892578125</v>
       </c>
+      <c r="V4">
+        <v>39.87</v>
+      </c>
     </row>
     <row r="5" spans="1:22">
       <c r="A5" s="1">
@@ -689,6 +692,9 @@
       <c r="D5">
         <v>44.679931640625</v>
       </c>
+      <c r="V5">
+        <v>69.06999999999999</v>
+      </c>
     </row>
     <row r="6" spans="1:22">
       <c r="A6" s="1">
@@ -725,10 +731,10 @@
         <v>85.85009765625</v>
       </c>
       <c r="L6">
-        <v>58.090087890625</v>
-      </c>
-      <c r="M6">
-        <v>58.090087890625</v>
+        <v>85.85009765625</v>
+      </c>
+      <c r="V6">
+        <v>59.29</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -765,6 +771,9 @@
       <c r="K7">
         <v>39.699951171875</v>
       </c>
+      <c r="V7">
+        <v>32.15</v>
+      </c>
     </row>
     <row r="8" spans="1:22">
       <c r="A8" s="1">
@@ -801,7 +810,10 @@
         <v>49.760009765625</v>
       </c>
       <c r="L8">
-        <v>38.780029296875</v>
+        <v>49.760009765625</v>
+      </c>
+      <c r="V8">
+        <v>39.58</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -839,10 +851,10 @@
         <v>59.010009765625</v>
       </c>
       <c r="L9">
-        <v>60.169921875</v>
-      </c>
-      <c r="M9">
-        <v>60.169921875</v>
+        <v>59.010009765625</v>
+      </c>
+      <c r="V9">
+        <v>60.57</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -880,10 +892,10 @@
         <v>66.93994140625</v>
       </c>
       <c r="L10">
-        <v>58.949951171875</v>
-      </c>
-      <c r="M10">
-        <v>58.949951171875</v>
+        <v>66.93994140625</v>
+      </c>
+      <c r="V10">
+        <v>59.75</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -902,6 +914,9 @@
       <c r="E11">
         <v>42.14990234375</v>
       </c>
+      <c r="V11">
+        <v>19.4</v>
+      </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1">
@@ -938,10 +953,10 @@
         <v>70.10009765625</v>
       </c>
       <c r="L12">
-        <v>42.090087890625</v>
-      </c>
-      <c r="M12">
-        <v>42.090087890625</v>
+        <v>70.10009765625</v>
+      </c>
+      <c r="V12">
+        <v>42.89</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -954,6 +969,9 @@
       <c r="C13">
         <v>0</v>
       </c>
+      <c r="V13">
+        <v>67.78</v>
+      </c>
     </row>
     <row r="14" spans="1:22">
       <c r="A14" s="1">
@@ -990,10 +1008,10 @@
         <v>62.89990234375</v>
       </c>
       <c r="L14">
-        <v>43.25</v>
-      </c>
-      <c r="M14">
-        <v>43.25</v>
+        <v>62.89990234375</v>
+      </c>
+      <c r="V14">
+        <v>44.05</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -1018,6 +1036,9 @@
       <c r="G15">
         <v>41.169921875</v>
       </c>
+      <c r="V15">
+        <v>54.48</v>
+      </c>
     </row>
     <row r="16" spans="1:22">
       <c r="A16" s="1">
@@ -1047,8 +1068,11 @@
       <c r="I16">
         <v>48.469970703125</v>
       </c>
-    </row>
-    <row r="17" spans="1:13">
+      <c r="V16">
+        <v>55.58</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22">
       <c r="A17" s="1">
         <v>19209079</v>
       </c>
@@ -1083,13 +1107,13 @@
         <v>87.14013671875</v>
       </c>
       <c r="L17">
-        <v>55.27001953125</v>
-      </c>
-      <c r="M17">
-        <v>55.27001953125</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13">
+        <v>87.14013671875</v>
+      </c>
+      <c r="V17">
+        <v>56.47</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22">
       <c r="A18" s="1">
         <v>19833277</v>
       </c>
@@ -1124,10 +1148,13 @@
         <v>73.68017578125</v>
       </c>
       <c r="L18">
-        <v>30.3699951171875</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13">
+        <v>73.68017578125</v>
+      </c>
+      <c r="V18">
+        <v>31.57</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22">
       <c r="A19" s="1">
         <v>20651178</v>
       </c>
@@ -1146,8 +1173,11 @@
       <c r="F19">
         <v>42.56005859375</v>
       </c>
-    </row>
-    <row r="20" spans="1:13">
+      <c r="V19">
+        <v>60.45</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22">
       <c r="A20" s="1">
         <v>44810918</v>
       </c>
@@ -1182,13 +1212,13 @@
         <v>104.68017578125</v>
       </c>
       <c r="L20">
-        <v>66.89013671875</v>
-      </c>
-      <c r="M20">
-        <v>66.89013671875</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13">
+        <v>104.68017578125</v>
+      </c>
+      <c r="V20">
+        <v>67.29000000000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22">
       <c r="A21" s="1">
         <v>47775950</v>
       </c>
@@ -1218,6 +1248,9 @@
       </c>
       <c r="J21">
         <v>42.89990234375</v>
+      </c>
+      <c r="V21">
+        <v>66.56999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao_20.xlsx
+++ b/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao_20.xlsx
@@ -76,7 +76,7 @@
     <t>Rodada 19</t>
   </si>
   <si>
-    <t>Parcial Rodada 10</t>
+    <t>Parcial Rodada 11</t>
   </si>
   <si>
     <t>time_id</t>
@@ -603,10 +603,10 @@
         <v>85.93994140625</v>
       </c>
       <c r="L2">
-        <v>85.93994140625</v>
-      </c>
-      <c r="V2">
-        <v>43.59</v>
+        <v>43.590087890625</v>
+      </c>
+      <c r="M2">
+        <v>43.590087890625</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -644,10 +644,10 @@
         <v>94.27978515625</v>
       </c>
       <c r="L3">
-        <v>94.27978515625</v>
-      </c>
-      <c r="V3">
-        <v>71.17</v>
+        <v>70.77001953125</v>
+      </c>
+      <c r="M3">
+        <v>70.77001953125</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -675,9 +675,6 @@
       <c r="H4">
         <v>47.389892578125</v>
       </c>
-      <c r="V4">
-        <v>39.87</v>
-      </c>
     </row>
     <row r="5" spans="1:22">
       <c r="A5" s="1">
@@ -692,9 +689,6 @@
       <c r="D5">
         <v>44.679931640625</v>
       </c>
-      <c r="V5">
-        <v>69.06999999999999</v>
-      </c>
     </row>
     <row r="6" spans="1:22">
       <c r="A6" s="1">
@@ -731,10 +725,10 @@
         <v>85.85009765625</v>
       </c>
       <c r="L6">
-        <v>85.85009765625</v>
-      </c>
-      <c r="V6">
-        <v>59.29</v>
+        <v>58.090087890625</v>
+      </c>
+      <c r="M6">
+        <v>58.090087890625</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -771,9 +765,6 @@
       <c r="K7">
         <v>39.699951171875</v>
       </c>
-      <c r="V7">
-        <v>32.15</v>
-      </c>
     </row>
     <row r="8" spans="1:22">
       <c r="A8" s="1">
@@ -810,10 +801,10 @@
         <v>49.760009765625</v>
       </c>
       <c r="L8">
-        <v>49.760009765625</v>
-      </c>
-      <c r="V8">
-        <v>39.58</v>
+        <v>38.780029296875</v>
+      </c>
+      <c r="M8">
+        <v>38.780029296875</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -851,10 +842,10 @@
         <v>59.010009765625</v>
       </c>
       <c r="L9">
-        <v>59.010009765625</v>
-      </c>
-      <c r="V9">
-        <v>60.57</v>
+        <v>60.169921875</v>
+      </c>
+      <c r="M9">
+        <v>60.169921875</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -892,10 +883,10 @@
         <v>66.93994140625</v>
       </c>
       <c r="L10">
-        <v>66.93994140625</v>
-      </c>
-      <c r="V10">
-        <v>59.75</v>
+        <v>58.949951171875</v>
+      </c>
+      <c r="M10">
+        <v>58.949951171875</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -914,9 +905,6 @@
       <c r="E11">
         <v>42.14990234375</v>
       </c>
-      <c r="V11">
-        <v>19.4</v>
-      </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1">
@@ -953,10 +941,10 @@
         <v>70.10009765625</v>
       </c>
       <c r="L12">
-        <v>70.10009765625</v>
-      </c>
-      <c r="V12">
-        <v>42.89</v>
+        <v>42.090087890625</v>
+      </c>
+      <c r="M12">
+        <v>42.090087890625</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -969,9 +957,6 @@
       <c r="C13">
         <v>0</v>
       </c>
-      <c r="V13">
-        <v>67.78</v>
-      </c>
     </row>
     <row r="14" spans="1:22">
       <c r="A14" s="1">
@@ -1008,10 +993,10 @@
         <v>62.89990234375</v>
       </c>
       <c r="L14">
-        <v>62.89990234375</v>
-      </c>
-      <c r="V14">
-        <v>44.05</v>
+        <v>43.25</v>
+      </c>
+      <c r="M14">
+        <v>43.25</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -1036,9 +1021,6 @@
       <c r="G15">
         <v>41.169921875</v>
       </c>
-      <c r="V15">
-        <v>54.48</v>
-      </c>
     </row>
     <row r="16" spans="1:22">
       <c r="A16" s="1">
@@ -1068,11 +1050,8 @@
       <c r="I16">
         <v>48.469970703125</v>
       </c>
-      <c r="V16">
-        <v>55.58</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22">
+    </row>
+    <row r="17" spans="1:13">
       <c r="A17" s="1">
         <v>19209079</v>
       </c>
@@ -1107,13 +1086,13 @@
         <v>87.14013671875</v>
       </c>
       <c r="L17">
-        <v>87.14013671875</v>
-      </c>
-      <c r="V17">
-        <v>56.47</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22">
+        <v>55.27001953125</v>
+      </c>
+      <c r="M17">
+        <v>55.27001953125</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
       <c r="A18" s="1">
         <v>19833277</v>
       </c>
@@ -1148,13 +1127,10 @@
         <v>73.68017578125</v>
       </c>
       <c r="L18">
-        <v>73.68017578125</v>
-      </c>
-      <c r="V18">
-        <v>31.57</v>
-      </c>
-    </row>
-    <row r="19" spans="1:22">
+        <v>30.3699951171875</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
       <c r="A19" s="1">
         <v>20651178</v>
       </c>
@@ -1173,11 +1149,8 @@
       <c r="F19">
         <v>42.56005859375</v>
       </c>
-      <c r="V19">
-        <v>60.45</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22">
+    </row>
+    <row r="20" spans="1:13">
       <c r="A20" s="1">
         <v>44810918</v>
       </c>
@@ -1212,13 +1185,13 @@
         <v>104.68017578125</v>
       </c>
       <c r="L20">
-        <v>104.68017578125</v>
-      </c>
-      <c r="V20">
-        <v>67.29000000000001</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22">
+        <v>66.89013671875</v>
+      </c>
+      <c r="M20">
+        <v>66.89013671875</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
       <c r="A21" s="1">
         <v>47775950</v>
       </c>
@@ -1248,9 +1221,6 @@
       </c>
       <c r="J21">
         <v>42.89990234375</v>
-      </c>
-      <c r="V21">
-        <v>66.56999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao_20.xlsx
+++ b/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao_20.xlsx
@@ -76,7 +76,7 @@
     <t>Rodada 19</t>
   </si>
   <si>
-    <t>Parcial Rodada 11</t>
+    <t>Parcial Rodada 12</t>
   </si>
   <si>
     <t>time_id</t>
@@ -606,7 +606,10 @@
         <v>43.590087890625</v>
       </c>
       <c r="M2">
-        <v>43.590087890625</v>
+        <v>86.9599609375</v>
+      </c>
+      <c r="N2">
+        <v>86.9599609375</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -647,7 +650,10 @@
         <v>70.77001953125</v>
       </c>
       <c r="M3">
-        <v>70.77001953125</v>
+        <v>98.56005859375</v>
+      </c>
+      <c r="N3">
+        <v>98.56005859375</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -728,7 +734,10 @@
         <v>58.090087890625</v>
       </c>
       <c r="M6">
-        <v>58.090087890625</v>
+        <v>88.759765625</v>
+      </c>
+      <c r="N6">
+        <v>88.759765625</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -804,7 +813,10 @@
         <v>38.780029296875</v>
       </c>
       <c r="M8">
-        <v>38.780029296875</v>
+        <v>88.06005859375</v>
+      </c>
+      <c r="N8">
+        <v>88.06005859375</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -845,7 +857,10 @@
         <v>60.169921875</v>
       </c>
       <c r="M9">
-        <v>60.169921875</v>
+        <v>82.81005859375</v>
+      </c>
+      <c r="N9">
+        <v>82.81005859375</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -886,7 +901,10 @@
         <v>58.949951171875</v>
       </c>
       <c r="M10">
-        <v>58.949951171875</v>
+        <v>92.66015625</v>
+      </c>
+      <c r="N10">
+        <v>92.66015625</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -944,7 +962,7 @@
         <v>42.090087890625</v>
       </c>
       <c r="M12">
-        <v>42.090087890625</v>
+        <v>70.9599609375</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -996,7 +1014,10 @@
         <v>43.25</v>
       </c>
       <c r="M14">
-        <v>43.25</v>
+        <v>81.8798828125</v>
+      </c>
+      <c r="N14">
+        <v>81.8798828125</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -1051,7 +1072,7 @@
         <v>48.469970703125</v>
       </c>
     </row>
-    <row r="17" spans="1:13">
+    <row r="17" spans="1:14">
       <c r="A17" s="1">
         <v>19209079</v>
       </c>
@@ -1089,10 +1110,13 @@
         <v>55.27001953125</v>
       </c>
       <c r="M17">
-        <v>55.27001953125</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13">
+        <v>81.35986328125</v>
+      </c>
+      <c r="N17">
+        <v>81.35986328125</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
       <c r="A18" s="1">
         <v>19833277</v>
       </c>
@@ -1130,7 +1154,7 @@
         <v>30.3699951171875</v>
       </c>
     </row>
-    <row r="19" spans="1:13">
+    <row r="19" spans="1:14">
       <c r="A19" s="1">
         <v>20651178</v>
       </c>
@@ -1150,7 +1174,7 @@
         <v>42.56005859375</v>
       </c>
     </row>
-    <row r="20" spans="1:13">
+    <row r="20" spans="1:14">
       <c r="A20" s="1">
         <v>44810918</v>
       </c>
@@ -1188,10 +1212,13 @@
         <v>66.89013671875</v>
       </c>
       <c r="M20">
-        <v>66.89013671875</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13">
+        <v>90.4599609375</v>
+      </c>
+      <c r="N20">
+        <v>90.4599609375</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
       <c r="A21" s="1">
         <v>47775950</v>
       </c>

--- a/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao_20.xlsx
+++ b/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao_20.xlsx
@@ -611,6 +611,9 @@
       <c r="N2">
         <v>86.9599609375</v>
       </c>
+      <c r="V2">
+        <v>101.25</v>
+      </c>
     </row>
     <row r="3" spans="1:22">
       <c r="A3" s="1">
@@ -655,6 +658,9 @@
       <c r="N3">
         <v>98.56005859375</v>
       </c>
+      <c r="V3">
+        <v>83.5</v>
+      </c>
     </row>
     <row r="4" spans="1:22">
       <c r="A4" s="1">
@@ -681,6 +687,9 @@
       <c r="H4">
         <v>47.389892578125</v>
       </c>
+      <c r="V4">
+        <v>81.45</v>
+      </c>
     </row>
     <row r="5" spans="1:22">
       <c r="A5" s="1">
@@ -695,6 +704,9 @@
       <c r="D5">
         <v>44.679931640625</v>
       </c>
+      <c r="V5">
+        <v>66.40000000000001</v>
+      </c>
     </row>
     <row r="6" spans="1:22">
       <c r="A6" s="1">
@@ -739,6 +751,9 @@
       <c r="N6">
         <v>88.759765625</v>
       </c>
+      <c r="V6">
+        <v>86.66</v>
+      </c>
     </row>
     <row r="7" spans="1:22">
       <c r="A7" s="1">
@@ -774,6 +789,9 @@
       <c r="K7">
         <v>39.699951171875</v>
       </c>
+      <c r="V7">
+        <v>35.29</v>
+      </c>
     </row>
     <row r="8" spans="1:22">
       <c r="A8" s="1">
@@ -818,6 +836,9 @@
       <c r="N8">
         <v>88.06005859375</v>
       </c>
+      <c r="V8">
+        <v>65.84999999999999</v>
+      </c>
     </row>
     <row r="9" spans="1:22">
       <c r="A9" s="1">
@@ -862,6 +883,9 @@
       <c r="N9">
         <v>82.81005859375</v>
       </c>
+      <c r="V9">
+        <v>77.34999999999999</v>
+      </c>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" s="1">
@@ -906,6 +930,9 @@
       <c r="N10">
         <v>92.66015625</v>
       </c>
+      <c r="V10">
+        <v>76.8</v>
+      </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="1">
@@ -923,6 +950,9 @@
       <c r="E11">
         <v>42.14990234375</v>
       </c>
+      <c r="V11">
+        <v>72.09999999999999</v>
+      </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1">
@@ -964,6 +994,9 @@
       <c r="M12">
         <v>70.9599609375</v>
       </c>
+      <c r="V12">
+        <v>100</v>
+      </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="1">
@@ -975,6 +1008,9 @@
       <c r="C13">
         <v>0</v>
       </c>
+      <c r="V13">
+        <v>57.1</v>
+      </c>
     </row>
     <row r="14" spans="1:22">
       <c r="A14" s="1">
@@ -1019,6 +1055,9 @@
       <c r="N14">
         <v>81.8798828125</v>
       </c>
+      <c r="V14">
+        <v>41.57</v>
+      </c>
     </row>
     <row r="15" spans="1:22">
       <c r="A15" s="1">
@@ -1042,6 +1081,9 @@
       <c r="G15">
         <v>41.169921875</v>
       </c>
+      <c r="V15">
+        <v>64.92</v>
+      </c>
     </row>
     <row r="16" spans="1:22">
       <c r="A16" s="1">
@@ -1071,8 +1113,11 @@
       <c r="I16">
         <v>48.469970703125</v>
       </c>
-    </row>
-    <row r="17" spans="1:14">
+      <c r="V16">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22">
       <c r="A17" s="1">
         <v>19209079</v>
       </c>
@@ -1115,8 +1160,11 @@
       <c r="N17">
         <v>81.35986328125</v>
       </c>
-    </row>
-    <row r="18" spans="1:14">
+      <c r="V17">
+        <v>68.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22">
       <c r="A18" s="1">
         <v>19833277</v>
       </c>
@@ -1153,8 +1201,11 @@
       <c r="L18">
         <v>30.3699951171875</v>
       </c>
-    </row>
-    <row r="19" spans="1:14">
+      <c r="V18">
+        <v>66.11</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22">
       <c r="A19" s="1">
         <v>20651178</v>
       </c>
@@ -1173,8 +1224,11 @@
       <c r="F19">
         <v>42.56005859375</v>
       </c>
-    </row>
-    <row r="20" spans="1:14">
+      <c r="V19">
+        <v>81.95</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22">
       <c r="A20" s="1">
         <v>44810918</v>
       </c>
@@ -1217,8 +1271,11 @@
       <c r="N20">
         <v>90.4599609375</v>
       </c>
-    </row>
-    <row r="21" spans="1:14">
+      <c r="V20">
+        <v>84.40000000000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22">
       <c r="A21" s="1">
         <v>47775950</v>
       </c>
@@ -1248,6 +1305,9 @@
       </c>
       <c r="J21">
         <v>42.89990234375</v>
+      </c>
+      <c r="V21">
+        <v>69.90000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao_20.xlsx
+++ b/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao_20.xlsx
@@ -76,7 +76,7 @@
     <t>Rodada 19</t>
   </si>
   <si>
-    <t>Parcial Rodada 12</t>
+    <t>Parcial Rodada 13</t>
   </si>
   <si>
     <t>time_id</t>
@@ -609,9 +609,9 @@
         <v>86.9599609375</v>
       </c>
       <c r="N2">
-        <v>86.9599609375</v>
-      </c>
-      <c r="V2">
+        <v>101.25</v>
+      </c>
+      <c r="O2">
         <v>101.25</v>
       </c>
     </row>
@@ -656,9 +656,9 @@
         <v>98.56005859375</v>
       </c>
       <c r="N3">
-        <v>98.56005859375</v>
-      </c>
-      <c r="V3">
+        <v>83.5</v>
+      </c>
+      <c r="O3">
         <v>83.5</v>
       </c>
     </row>
@@ -687,9 +687,6 @@
       <c r="H4">
         <v>47.389892578125</v>
       </c>
-      <c r="V4">
-        <v>81.45</v>
-      </c>
     </row>
     <row r="5" spans="1:22">
       <c r="A5" s="1">
@@ -704,9 +701,6 @@
       <c r="D5">
         <v>44.679931640625</v>
       </c>
-      <c r="V5">
-        <v>66.40000000000001</v>
-      </c>
     </row>
     <row r="6" spans="1:22">
       <c r="A6" s="1">
@@ -749,10 +743,10 @@
         <v>88.759765625</v>
       </c>
       <c r="N6">
-        <v>88.759765625</v>
-      </c>
-      <c r="V6">
-        <v>86.66</v>
+        <v>86.66015625</v>
+      </c>
+      <c r="O6">
+        <v>86.66015625</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -789,9 +783,6 @@
       <c r="K7">
         <v>39.699951171875</v>
       </c>
-      <c r="V7">
-        <v>35.29</v>
-      </c>
     </row>
     <row r="8" spans="1:22">
       <c r="A8" s="1">
@@ -834,10 +825,10 @@
         <v>88.06005859375</v>
       </c>
       <c r="N8">
-        <v>88.06005859375</v>
-      </c>
-      <c r="V8">
-        <v>65.84999999999999</v>
+        <v>65.85009765625</v>
+      </c>
+      <c r="O8">
+        <v>65.85009765625</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -881,10 +872,10 @@
         <v>82.81005859375</v>
       </c>
       <c r="N9">
-        <v>82.81005859375</v>
-      </c>
-      <c r="V9">
-        <v>77.34999999999999</v>
+        <v>77.35009765625</v>
+      </c>
+      <c r="O9">
+        <v>77.35009765625</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -928,10 +919,10 @@
         <v>92.66015625</v>
       </c>
       <c r="N10">
-        <v>92.66015625</v>
-      </c>
-      <c r="V10">
-        <v>76.8</v>
+        <v>76.7998046875</v>
+      </c>
+      <c r="O10">
+        <v>76.7998046875</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -950,9 +941,6 @@
       <c r="E11">
         <v>42.14990234375</v>
       </c>
-      <c r="V11">
-        <v>72.09999999999999</v>
-      </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1">
@@ -994,9 +982,6 @@
       <c r="M12">
         <v>70.9599609375</v>
       </c>
-      <c r="V12">
-        <v>100</v>
-      </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="1">
@@ -1008,9 +993,6 @@
       <c r="C13">
         <v>0</v>
       </c>
-      <c r="V13">
-        <v>57.1</v>
-      </c>
     </row>
     <row r="14" spans="1:22">
       <c r="A14" s="1">
@@ -1053,10 +1035,7 @@
         <v>81.8798828125</v>
       </c>
       <c r="N14">
-        <v>81.8798828125</v>
-      </c>
-      <c r="V14">
-        <v>41.57</v>
+        <v>41.570068359375</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -1081,9 +1060,6 @@
       <c r="G15">
         <v>41.169921875</v>
       </c>
-      <c r="V15">
-        <v>64.92</v>
-      </c>
     </row>
     <row r="16" spans="1:22">
       <c r="A16" s="1">
@@ -1113,11 +1089,8 @@
       <c r="I16">
         <v>48.469970703125</v>
       </c>
-      <c r="V16">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22">
+    </row>
+    <row r="17" spans="1:15">
       <c r="A17" s="1">
         <v>19209079</v>
       </c>
@@ -1158,13 +1131,13 @@
         <v>81.35986328125</v>
       </c>
       <c r="N17">
-        <v>81.35986328125</v>
-      </c>
-      <c r="V17">
         <v>68.5</v>
       </c>
-    </row>
-    <row r="18" spans="1:22">
+      <c r="O17">
+        <v>68.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15">
       <c r="A18" s="1">
         <v>19833277</v>
       </c>
@@ -1201,11 +1174,8 @@
       <c r="L18">
         <v>30.3699951171875</v>
       </c>
-      <c r="V18">
-        <v>66.11</v>
-      </c>
-    </row>
-    <row r="19" spans="1:22">
+    </row>
+    <row r="19" spans="1:15">
       <c r="A19" s="1">
         <v>20651178</v>
       </c>
@@ -1224,11 +1194,8 @@
       <c r="F19">
         <v>42.56005859375</v>
       </c>
-      <c r="V19">
-        <v>81.95</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22">
+    </row>
+    <row r="20" spans="1:15">
       <c r="A20" s="1">
         <v>44810918</v>
       </c>
@@ -1269,13 +1236,13 @@
         <v>90.4599609375</v>
       </c>
       <c r="N20">
-        <v>90.4599609375</v>
-      </c>
-      <c r="V20">
-        <v>84.40000000000001</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22">
+        <v>84.39990234375</v>
+      </c>
+      <c r="O20">
+        <v>84.39990234375</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15">
       <c r="A21" s="1">
         <v>47775950</v>
       </c>
@@ -1305,9 +1272,6 @@
       </c>
       <c r="J21">
         <v>42.89990234375</v>
-      </c>
-      <c r="V21">
-        <v>69.90000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao_20.xlsx
+++ b/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao_20.xlsx
@@ -614,6 +614,9 @@
       <c r="O2">
         <v>101.25</v>
       </c>
+      <c r="V2">
+        <v>90.02</v>
+      </c>
     </row>
     <row r="3" spans="1:22">
       <c r="A3" s="1">
@@ -661,6 +664,9 @@
       <c r="O3">
         <v>83.5</v>
       </c>
+      <c r="V3">
+        <v>114.52</v>
+      </c>
     </row>
     <row r="4" spans="1:22">
       <c r="A4" s="1">
@@ -687,6 +693,9 @@
       <c r="H4">
         <v>47.389892578125</v>
       </c>
+      <c r="V4">
+        <v>113.22</v>
+      </c>
     </row>
     <row r="5" spans="1:22">
       <c r="A5" s="1">
@@ -701,6 +710,9 @@
       <c r="D5">
         <v>44.679931640625</v>
       </c>
+      <c r="V5">
+        <v>102.42</v>
+      </c>
     </row>
     <row r="6" spans="1:22">
       <c r="A6" s="1">
@@ -748,6 +760,9 @@
       <c r="O6">
         <v>86.66015625</v>
       </c>
+      <c r="V6">
+        <v>97.62</v>
+      </c>
     </row>
     <row r="7" spans="1:22">
       <c r="A7" s="1">
@@ -783,6 +798,9 @@
       <c r="K7">
         <v>39.699951171875</v>
       </c>
+      <c r="V7">
+        <v>53.33</v>
+      </c>
     </row>
     <row r="8" spans="1:22">
       <c r="A8" s="1">
@@ -830,6 +848,9 @@
       <c r="O8">
         <v>65.85009765625</v>
       </c>
+      <c r="V8">
+        <v>90.37</v>
+      </c>
     </row>
     <row r="9" spans="1:22">
       <c r="A9" s="1">
@@ -877,6 +898,9 @@
       <c r="O9">
         <v>77.35009765625</v>
       </c>
+      <c r="V9">
+        <v>91.87</v>
+      </c>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" s="1">
@@ -924,6 +948,9 @@
       <c r="O10">
         <v>76.7998046875</v>
       </c>
+      <c r="V10">
+        <v>85.94</v>
+      </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="1">
@@ -941,6 +968,9 @@
       <c r="E11">
         <v>42.14990234375</v>
       </c>
+      <c r="V11">
+        <v>119.03</v>
+      </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1">
@@ -982,6 +1012,9 @@
       <c r="M12">
         <v>70.9599609375</v>
       </c>
+      <c r="V12">
+        <v>92.52</v>
+      </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="1">
@@ -993,6 +1026,9 @@
       <c r="C13">
         <v>0</v>
       </c>
+      <c r="V13">
+        <v>31.05</v>
+      </c>
     </row>
     <row r="14" spans="1:22">
       <c r="A14" s="1">
@@ -1037,6 +1073,9 @@
       <c r="N14">
         <v>41.570068359375</v>
       </c>
+      <c r="V14">
+        <v>96.77</v>
+      </c>
     </row>
     <row r="15" spans="1:22">
       <c r="A15" s="1">
@@ -1060,6 +1099,9 @@
       <c r="G15">
         <v>41.169921875</v>
       </c>
+      <c r="V15">
+        <v>99.97</v>
+      </c>
     </row>
     <row r="16" spans="1:22">
       <c r="A16" s="1">
@@ -1089,8 +1131,11 @@
       <c r="I16">
         <v>48.469970703125</v>
       </c>
-    </row>
-    <row r="17" spans="1:15">
+      <c r="V16">
+        <v>108.98</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22">
       <c r="A17" s="1">
         <v>19209079</v>
       </c>
@@ -1136,8 +1181,11 @@
       <c r="O17">
         <v>68.5</v>
       </c>
-    </row>
-    <row r="18" spans="1:15">
+      <c r="V17">
+        <v>88.47</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22">
       <c r="A18" s="1">
         <v>19833277</v>
       </c>
@@ -1174,8 +1222,11 @@
       <c r="L18">
         <v>30.3699951171875</v>
       </c>
-    </row>
-    <row r="19" spans="1:15">
+      <c r="V18">
+        <v>99.31999999999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22">
       <c r="A19" s="1">
         <v>20651178</v>
       </c>
@@ -1194,8 +1245,11 @@
       <c r="F19">
         <v>42.56005859375</v>
       </c>
-    </row>
-    <row r="20" spans="1:15">
+      <c r="V19">
+        <v>92.22</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22">
       <c r="A20" s="1">
         <v>44810918</v>
       </c>
@@ -1241,8 +1295,11 @@
       <c r="O20">
         <v>84.39990234375</v>
       </c>
-    </row>
-    <row r="21" spans="1:15">
+      <c r="V20">
+        <v>108.52</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22">
       <c r="A21" s="1">
         <v>47775950</v>
       </c>
@@ -1272,6 +1329,9 @@
       </c>
       <c r="J21">
         <v>42.89990234375</v>
+      </c>
+      <c r="V21">
+        <v>108.52</v>
       </c>
     </row>
   </sheetData>

--- a/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao_20.xlsx
+++ b/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao_20.xlsx
@@ -615,7 +615,7 @@
         <v>101.25</v>
       </c>
       <c r="V2">
-        <v>90.02</v>
+        <v>102.99</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -665,7 +665,7 @@
         <v>83.5</v>
       </c>
       <c r="V3">
-        <v>114.52</v>
+        <v>114.09</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -694,7 +694,7 @@
         <v>47.389892578125</v>
       </c>
       <c r="V4">
-        <v>113.22</v>
+        <v>113.29</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -711,7 +711,7 @@
         <v>44.679931640625</v>
       </c>
       <c r="V5">
-        <v>102.42</v>
+        <v>112.29</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -761,7 +761,7 @@
         <v>86.66015625</v>
       </c>
       <c r="V6">
-        <v>97.62</v>
+        <v>106.39</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -799,7 +799,7 @@
         <v>39.699951171875</v>
       </c>
       <c r="V7">
-        <v>53.33</v>
+        <v>54.83</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -849,7 +849,7 @@
         <v>65.85009765625</v>
       </c>
       <c r="V8">
-        <v>90.37</v>
+        <v>98.44</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -899,7 +899,7 @@
         <v>77.35009765625</v>
       </c>
       <c r="V9">
-        <v>91.87</v>
+        <v>115.44</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -969,7 +969,7 @@
         <v>42.14990234375</v>
       </c>
       <c r="V11">
-        <v>119.03</v>
+        <v>118.53</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1013,7 +1013,7 @@
         <v>70.9599609375</v>
       </c>
       <c r="V12">
-        <v>92.52</v>
+        <v>100.59</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -1074,7 +1074,7 @@
         <v>41.570068359375</v>
       </c>
       <c r="V14">
-        <v>96.77</v>
+        <v>96.84</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -1100,7 +1100,7 @@
         <v>41.169921875</v>
       </c>
       <c r="V15">
-        <v>99.97</v>
+        <v>118.24</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -1132,7 +1132,7 @@
         <v>48.469970703125</v>
       </c>
       <c r="V16">
-        <v>108.98</v>
+        <v>108.48</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -1182,7 +1182,7 @@
         <v>68.5</v>
       </c>
       <c r="V17">
-        <v>88.47</v>
+        <v>88.04000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -1223,7 +1223,7 @@
         <v>30.3699951171875</v>
       </c>
       <c r="V18">
-        <v>99.31999999999999</v>
+        <v>99.39</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -1246,7 +1246,7 @@
         <v>42.56005859375</v>
       </c>
       <c r="V19">
-        <v>92.22</v>
+        <v>113.19</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -1296,7 +1296,7 @@
         <v>84.39990234375</v>
       </c>
       <c r="V20">
-        <v>108.52</v>
+        <v>108.59</v>
       </c>
     </row>
     <row r="21" spans="1:22">
@@ -1331,7 +1331,7 @@
         <v>42.89990234375</v>
       </c>
       <c r="V21">
-        <v>108.52</v>
+        <v>108.59</v>
       </c>
     </row>
   </sheetData>

--- a/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao_20.xlsx
+++ b/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao_20.xlsx
@@ -76,7 +76,7 @@
     <t>Rodada 19</t>
   </si>
   <si>
-    <t>Parcial Rodada 13</t>
+    <t>Parcial Rodada 14</t>
   </si>
   <si>
     <t>time_id</t>
@@ -612,10 +612,10 @@
         <v>101.25</v>
       </c>
       <c r="O2">
-        <v>101.25</v>
-      </c>
-      <c r="V2">
-        <v>102.99</v>
+        <v>102.990234375</v>
+      </c>
+      <c r="P2">
+        <v>102.990234375</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -662,10 +662,10 @@
         <v>83.5</v>
       </c>
       <c r="O3">
-        <v>83.5</v>
-      </c>
-      <c r="V3">
-        <v>114.09</v>
+        <v>114.08984375</v>
+      </c>
+      <c r="P3">
+        <v>114.08984375</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -693,9 +693,6 @@
       <c r="H4">
         <v>47.389892578125</v>
       </c>
-      <c r="V4">
-        <v>113.29</v>
-      </c>
     </row>
     <row r="5" spans="1:22">
       <c r="A5" s="1">
@@ -710,9 +707,6 @@
       <c r="D5">
         <v>44.679931640625</v>
       </c>
-      <c r="V5">
-        <v>112.29</v>
-      </c>
     </row>
     <row r="6" spans="1:22">
       <c r="A6" s="1">
@@ -758,10 +752,10 @@
         <v>86.66015625</v>
       </c>
       <c r="O6">
-        <v>86.66015625</v>
-      </c>
-      <c r="V6">
-        <v>106.39</v>
+        <v>106.39013671875</v>
+      </c>
+      <c r="P6">
+        <v>106.39013671875</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -798,9 +792,6 @@
       <c r="K7">
         <v>39.699951171875</v>
       </c>
-      <c r="V7">
-        <v>54.83</v>
-      </c>
     </row>
     <row r="8" spans="1:22">
       <c r="A8" s="1">
@@ -846,10 +837,10 @@
         <v>65.85009765625</v>
       </c>
       <c r="O8">
-        <v>65.85009765625</v>
-      </c>
-      <c r="V8">
-        <v>98.44</v>
+        <v>98.43994140625</v>
+      </c>
+      <c r="P8">
+        <v>98.43994140625</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -896,10 +887,10 @@
         <v>77.35009765625</v>
       </c>
       <c r="O9">
-        <v>77.35009765625</v>
-      </c>
-      <c r="V9">
-        <v>115.44</v>
+        <v>115.43994140625</v>
+      </c>
+      <c r="P9">
+        <v>115.43994140625</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -946,10 +937,7 @@
         <v>76.7998046875</v>
       </c>
       <c r="O10">
-        <v>76.7998046875</v>
-      </c>
-      <c r="V10">
-        <v>85.94</v>
+        <v>85.93994140625</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -968,9 +956,6 @@
       <c r="E11">
         <v>42.14990234375</v>
       </c>
-      <c r="V11">
-        <v>118.53</v>
-      </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1">
@@ -1012,9 +997,6 @@
       <c r="M12">
         <v>70.9599609375</v>
       </c>
-      <c r="V12">
-        <v>100.59</v>
-      </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="1">
@@ -1026,9 +1008,6 @@
       <c r="C13">
         <v>0</v>
       </c>
-      <c r="V13">
-        <v>31.05</v>
-      </c>
     </row>
     <row r="14" spans="1:22">
       <c r="A14" s="1">
@@ -1073,9 +1052,6 @@
       <c r="N14">
         <v>41.570068359375</v>
       </c>
-      <c r="V14">
-        <v>96.84</v>
-      </c>
     </row>
     <row r="15" spans="1:22">
       <c r="A15" s="1">
@@ -1099,9 +1075,6 @@
       <c r="G15">
         <v>41.169921875</v>
       </c>
-      <c r="V15">
-        <v>118.24</v>
-      </c>
     </row>
     <row r="16" spans="1:22">
       <c r="A16" s="1">
@@ -1131,11 +1104,8 @@
       <c r="I16">
         <v>48.469970703125</v>
       </c>
-      <c r="V16">
-        <v>108.48</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22">
+    </row>
+    <row r="17" spans="1:16">
       <c r="A17" s="1">
         <v>19209079</v>
       </c>
@@ -1179,13 +1149,13 @@
         <v>68.5</v>
       </c>
       <c r="O17">
-        <v>68.5</v>
-      </c>
-      <c r="V17">
-        <v>88.04000000000001</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22">
+        <v>88.0400390625</v>
+      </c>
+      <c r="P17">
+        <v>88.0400390625</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16">
       <c r="A18" s="1">
         <v>19833277</v>
       </c>
@@ -1222,11 +1192,8 @@
       <c r="L18">
         <v>30.3699951171875</v>
       </c>
-      <c r="V18">
-        <v>99.39</v>
-      </c>
-    </row>
-    <row r="19" spans="1:22">
+    </row>
+    <row r="19" spans="1:16">
       <c r="A19" s="1">
         <v>20651178</v>
       </c>
@@ -1245,11 +1212,8 @@
       <c r="F19">
         <v>42.56005859375</v>
       </c>
-      <c r="V19">
-        <v>113.19</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22">
+    </row>
+    <row r="20" spans="1:16">
       <c r="A20" s="1">
         <v>44810918</v>
       </c>
@@ -1293,13 +1257,13 @@
         <v>84.39990234375</v>
       </c>
       <c r="O20">
-        <v>84.39990234375</v>
-      </c>
-      <c r="V20">
-        <v>108.59</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22">
+        <v>108.58984375</v>
+      </c>
+      <c r="P20">
+        <v>108.58984375</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16">
       <c r="A21" s="1">
         <v>47775950</v>
       </c>
@@ -1329,9 +1293,6 @@
       </c>
       <c r="J21">
         <v>42.89990234375</v>
-      </c>
-      <c r="V21">
-        <v>108.59</v>
       </c>
     </row>
   </sheetData>

--- a/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao_20.xlsx
+++ b/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao_20.xlsx
@@ -76,7 +76,7 @@
     <t>Rodada 19</t>
   </si>
   <si>
-    <t>Parcial Rodada 14</t>
+    <t>Parcial Rodada 15</t>
   </si>
   <si>
     <t>time_id</t>
@@ -615,7 +615,10 @@
         <v>102.990234375</v>
       </c>
       <c r="P2">
-        <v>102.990234375</v>
+        <v>66.080078125</v>
+      </c>
+      <c r="Q2">
+        <v>66.080078125</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -665,7 +668,10 @@
         <v>114.08984375</v>
       </c>
       <c r="P3">
-        <v>114.08984375</v>
+        <v>57.14990234375</v>
+      </c>
+      <c r="Q3">
+        <v>57.14990234375</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -755,7 +761,10 @@
         <v>106.39013671875</v>
       </c>
       <c r="P6">
-        <v>106.39013671875</v>
+        <v>53.780029296875</v>
+      </c>
+      <c r="Q6">
+        <v>53.780029296875</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -840,7 +849,10 @@
         <v>98.43994140625</v>
       </c>
       <c r="P8">
-        <v>98.43994140625</v>
+        <v>78.4501953125</v>
+      </c>
+      <c r="Q8">
+        <v>78.4501953125</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -890,7 +902,10 @@
         <v>115.43994140625</v>
       </c>
       <c r="P9">
-        <v>115.43994140625</v>
+        <v>57.72998046875</v>
+      </c>
+      <c r="Q9">
+        <v>57.72998046875</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -1105,7 +1120,7 @@
         <v>48.469970703125</v>
       </c>
     </row>
-    <row r="17" spans="1:16">
+    <row r="17" spans="1:17">
       <c r="A17" s="1">
         <v>19209079</v>
       </c>
@@ -1152,10 +1167,13 @@
         <v>88.0400390625</v>
       </c>
       <c r="P17">
-        <v>88.0400390625</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16">
+        <v>69.4501953125</v>
+      </c>
+      <c r="Q17">
+        <v>69.4501953125</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17">
       <c r="A18" s="1">
         <v>19833277</v>
       </c>
@@ -1193,7 +1211,7 @@
         <v>30.3699951171875</v>
       </c>
     </row>
-    <row r="19" spans="1:16">
+    <row r="19" spans="1:17">
       <c r="A19" s="1">
         <v>20651178</v>
       </c>
@@ -1213,7 +1231,7 @@
         <v>42.56005859375</v>
       </c>
     </row>
-    <row r="20" spans="1:16">
+    <row r="20" spans="1:17">
       <c r="A20" s="1">
         <v>44810918</v>
       </c>
@@ -1260,10 +1278,10 @@
         <v>108.58984375</v>
       </c>
       <c r="P20">
-        <v>108.58984375</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16">
+        <v>49.280029296875</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17">
       <c r="A21" s="1">
         <v>47775950</v>
       </c>

--- a/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao_20.xlsx
+++ b/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao_20.xlsx
@@ -620,6 +620,9 @@
       <c r="Q2">
         <v>66.080078125</v>
       </c>
+      <c r="V2">
+        <v>49.62</v>
+      </c>
     </row>
     <row r="3" spans="1:22">
       <c r="A3" s="1">
@@ -673,6 +676,9 @@
       <c r="Q3">
         <v>57.14990234375</v>
       </c>
+      <c r="V3">
+        <v>53.93</v>
+      </c>
     </row>
     <row r="4" spans="1:22">
       <c r="A4" s="1">
@@ -699,6 +705,9 @@
       <c r="H4">
         <v>47.389892578125</v>
       </c>
+      <c r="V4">
+        <v>60.17</v>
+      </c>
     </row>
     <row r="5" spans="1:22">
       <c r="A5" s="1">
@@ -713,6 +722,9 @@
       <c r="D5">
         <v>44.679931640625</v>
       </c>
+      <c r="V5">
+        <v>58.04</v>
+      </c>
     </row>
     <row r="6" spans="1:22">
       <c r="A6" s="1">
@@ -766,6 +778,9 @@
       <c r="Q6">
         <v>53.780029296875</v>
       </c>
+      <c r="V6">
+        <v>63.75</v>
+      </c>
     </row>
     <row r="7" spans="1:22">
       <c r="A7" s="1">
@@ -801,6 +816,9 @@
       <c r="K7">
         <v>39.699951171875</v>
       </c>
+      <c r="V7">
+        <v>42.1</v>
+      </c>
     </row>
     <row r="8" spans="1:22">
       <c r="A8" s="1">
@@ -854,6 +872,9 @@
       <c r="Q8">
         <v>78.4501953125</v>
       </c>
+      <c r="V8">
+        <v>45.15</v>
+      </c>
     </row>
     <row r="9" spans="1:22">
       <c r="A9" s="1">
@@ -907,6 +928,9 @@
       <c r="Q9">
         <v>57.72998046875</v>
       </c>
+      <c r="V9">
+        <v>55.9</v>
+      </c>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" s="1">
@@ -954,6 +978,9 @@
       <c r="O10">
         <v>85.93994140625</v>
       </c>
+      <c r="V10">
+        <v>35.42</v>
+      </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="1">
@@ -971,6 +998,9 @@
       <c r="E11">
         <v>42.14990234375</v>
       </c>
+      <c r="V11">
+        <v>81.98</v>
+      </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1">
@@ -1012,6 +1042,9 @@
       <c r="M12">
         <v>70.9599609375</v>
       </c>
+      <c r="V12">
+        <v>39.12</v>
+      </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="1">
@@ -1023,6 +1056,9 @@
       <c r="C13">
         <v>0</v>
       </c>
+      <c r="V13">
+        <v>31.34</v>
+      </c>
     </row>
     <row r="14" spans="1:22">
       <c r="A14" s="1">
@@ -1067,6 +1103,9 @@
       <c r="N14">
         <v>41.570068359375</v>
       </c>
+      <c r="V14">
+        <v>52.2</v>
+      </c>
     </row>
     <row r="15" spans="1:22">
       <c r="A15" s="1">
@@ -1090,6 +1129,9 @@
       <c r="G15">
         <v>41.169921875</v>
       </c>
+      <c r="V15">
+        <v>50.2</v>
+      </c>
     </row>
     <row r="16" spans="1:22">
       <c r="A16" s="1">
@@ -1119,8 +1161,11 @@
       <c r="I16">
         <v>48.469970703125</v>
       </c>
-    </row>
-    <row r="17" spans="1:17">
+      <c r="V16">
+        <v>64.2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22">
       <c r="A17" s="1">
         <v>19209079</v>
       </c>
@@ -1172,8 +1217,11 @@
       <c r="Q17">
         <v>69.4501953125</v>
       </c>
-    </row>
-    <row r="18" spans="1:17">
+      <c r="V17">
+        <v>50.98</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22">
       <c r="A18" s="1">
         <v>19833277</v>
       </c>
@@ -1210,8 +1258,11 @@
       <c r="L18">
         <v>30.3699951171875</v>
       </c>
-    </row>
-    <row r="19" spans="1:17">
+      <c r="V18">
+        <v>45.78</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22">
       <c r="A19" s="1">
         <v>20651178</v>
       </c>
@@ -1230,8 +1281,11 @@
       <c r="F19">
         <v>42.56005859375</v>
       </c>
-    </row>
-    <row r="20" spans="1:17">
+      <c r="V19">
+        <v>45.92</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22">
       <c r="A20" s="1">
         <v>44810918</v>
       </c>
@@ -1280,8 +1334,11 @@
       <c r="P20">
         <v>49.280029296875</v>
       </c>
-    </row>
-    <row r="21" spans="1:17">
+      <c r="V20">
+        <v>54.58</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22">
       <c r="A21" s="1">
         <v>47775950</v>
       </c>
@@ -1311,6 +1368,9 @@
       </c>
       <c r="J21">
         <v>42.89990234375</v>
+      </c>
+      <c r="V21">
+        <v>55.52</v>
       </c>
     </row>
   </sheetData>

--- a/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao_20.xlsx
+++ b/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao_20.xlsx
@@ -76,7 +76,7 @@
     <t>Rodada 19</t>
   </si>
   <si>
-    <t>Parcial Rodada 15</t>
+    <t>Parcial Rodada 16</t>
   </si>
   <si>
     <t>time_id</t>
@@ -618,10 +618,10 @@
         <v>66.080078125</v>
       </c>
       <c r="Q2">
-        <v>66.080078125</v>
-      </c>
-      <c r="V2">
-        <v>49.62</v>
+        <v>49.6201171875</v>
+      </c>
+      <c r="R2">
+        <v>49.6201171875</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -674,10 +674,10 @@
         <v>57.14990234375</v>
       </c>
       <c r="Q3">
-        <v>57.14990234375</v>
-      </c>
-      <c r="V3">
-        <v>53.93</v>
+        <v>53.929931640625</v>
+      </c>
+      <c r="R3">
+        <v>53.929931640625</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -705,9 +705,6 @@
       <c r="H4">
         <v>47.389892578125</v>
       </c>
-      <c r="V4">
-        <v>60.17</v>
-      </c>
     </row>
     <row r="5" spans="1:22">
       <c r="A5" s="1">
@@ -722,9 +719,6 @@
       <c r="D5">
         <v>44.679931640625</v>
       </c>
-      <c r="V5">
-        <v>58.04</v>
-      </c>
     </row>
     <row r="6" spans="1:22">
       <c r="A6" s="1">
@@ -776,9 +770,9 @@
         <v>53.780029296875</v>
       </c>
       <c r="Q6">
-        <v>53.780029296875</v>
-      </c>
-      <c r="V6">
+        <v>63.75</v>
+      </c>
+      <c r="R6">
         <v>63.75</v>
       </c>
     </row>
@@ -816,9 +810,6 @@
       <c r="K7">
         <v>39.699951171875</v>
       </c>
-      <c r="V7">
-        <v>42.1</v>
-      </c>
     </row>
     <row r="8" spans="1:22">
       <c r="A8" s="1">
@@ -870,10 +861,7 @@
         <v>78.4501953125</v>
       </c>
       <c r="Q8">
-        <v>78.4501953125</v>
-      </c>
-      <c r="V8">
-        <v>45.15</v>
+        <v>45.14990234375</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -926,10 +914,10 @@
         <v>57.72998046875</v>
       </c>
       <c r="Q9">
-        <v>57.72998046875</v>
-      </c>
-      <c r="V9">
-        <v>55.9</v>
+        <v>55.89990234375</v>
+      </c>
+      <c r="R9">
+        <v>55.89990234375</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -978,9 +966,6 @@
       <c r="O10">
         <v>85.93994140625</v>
       </c>
-      <c r="V10">
-        <v>35.42</v>
-      </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="1">
@@ -998,9 +983,6 @@
       <c r="E11">
         <v>42.14990234375</v>
       </c>
-      <c r="V11">
-        <v>81.98</v>
-      </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1">
@@ -1042,9 +1024,6 @@
       <c r="M12">
         <v>70.9599609375</v>
       </c>
-      <c r="V12">
-        <v>39.12</v>
-      </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="1">
@@ -1056,9 +1035,6 @@
       <c r="C13">
         <v>0</v>
       </c>
-      <c r="V13">
-        <v>31.34</v>
-      </c>
     </row>
     <row r="14" spans="1:22">
       <c r="A14" s="1">
@@ -1103,9 +1079,6 @@
       <c r="N14">
         <v>41.570068359375</v>
       </c>
-      <c r="V14">
-        <v>52.2</v>
-      </c>
     </row>
     <row r="15" spans="1:22">
       <c r="A15" s="1">
@@ -1129,9 +1102,6 @@
       <c r="G15">
         <v>41.169921875</v>
       </c>
-      <c r="V15">
-        <v>50.2</v>
-      </c>
     </row>
     <row r="16" spans="1:22">
       <c r="A16" s="1">
@@ -1161,11 +1131,8 @@
       <c r="I16">
         <v>48.469970703125</v>
       </c>
-      <c r="V16">
-        <v>64.2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22">
+    </row>
+    <row r="17" spans="1:18">
       <c r="A17" s="1">
         <v>19209079</v>
       </c>
@@ -1215,13 +1182,13 @@
         <v>69.4501953125</v>
       </c>
       <c r="Q17">
-        <v>69.4501953125</v>
-      </c>
-      <c r="V17">
-        <v>50.98</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22">
+        <v>50.97998046875</v>
+      </c>
+      <c r="R17">
+        <v>50.97998046875</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18">
       <c r="A18" s="1">
         <v>19833277</v>
       </c>
@@ -1258,11 +1225,8 @@
       <c r="L18">
         <v>30.3699951171875</v>
       </c>
-      <c r="V18">
-        <v>45.78</v>
-      </c>
-    </row>
-    <row r="19" spans="1:22">
+    </row>
+    <row r="19" spans="1:18">
       <c r="A19" s="1">
         <v>20651178</v>
       </c>
@@ -1281,11 +1245,8 @@
       <c r="F19">
         <v>42.56005859375</v>
       </c>
-      <c r="V19">
-        <v>45.92</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22">
+    </row>
+    <row r="20" spans="1:18">
       <c r="A20" s="1">
         <v>44810918</v>
       </c>
@@ -1334,11 +1295,8 @@
       <c r="P20">
         <v>49.280029296875</v>
       </c>
-      <c r="V20">
-        <v>54.58</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22">
+    </row>
+    <row r="21" spans="1:18">
       <c r="A21" s="1">
         <v>47775950</v>
       </c>
@@ -1368,9 +1326,6 @@
       </c>
       <c r="J21">
         <v>42.89990234375</v>
-      </c>
-      <c r="V21">
-        <v>55.52</v>
       </c>
     </row>
   </sheetData>

--- a/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao_20.xlsx
+++ b/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao_20.xlsx
@@ -623,6 +623,9 @@
       <c r="R2">
         <v>49.6201171875</v>
       </c>
+      <c r="V2">
+        <v>76.28</v>
+      </c>
     </row>
     <row r="3" spans="1:22">
       <c r="A3" s="1">
@@ -679,6 +682,9 @@
       <c r="R3">
         <v>53.929931640625</v>
       </c>
+      <c r="V3">
+        <v>79.2</v>
+      </c>
     </row>
     <row r="4" spans="1:22">
       <c r="A4" s="1">
@@ -705,6 +711,9 @@
       <c r="H4">
         <v>47.389892578125</v>
       </c>
+      <c r="V4">
+        <v>72.28</v>
+      </c>
     </row>
     <row r="5" spans="1:22">
       <c r="A5" s="1">
@@ -719,6 +728,9 @@
       <c r="D5">
         <v>44.679931640625</v>
       </c>
+      <c r="V5">
+        <v>96.79000000000001</v>
+      </c>
     </row>
     <row r="6" spans="1:22">
       <c r="A6" s="1">
@@ -775,6 +787,9 @@
       <c r="R6">
         <v>63.75</v>
       </c>
+      <c r="V6">
+        <v>73.08</v>
+      </c>
     </row>
     <row r="7" spans="1:22">
       <c r="A7" s="1">
@@ -810,6 +825,9 @@
       <c r="K7">
         <v>39.699951171875</v>
       </c>
+      <c r="V7">
+        <v>19.51</v>
+      </c>
     </row>
     <row r="8" spans="1:22">
       <c r="A8" s="1">
@@ -863,6 +881,9 @@
       <c r="Q8">
         <v>45.14990234375</v>
       </c>
+      <c r="V8">
+        <v>105.5</v>
+      </c>
     </row>
     <row r="9" spans="1:22">
       <c r="A9" s="1">
@@ -919,6 +940,9 @@
       <c r="R9">
         <v>55.89990234375</v>
       </c>
+      <c r="V9">
+        <v>103.39</v>
+      </c>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" s="1">
@@ -966,6 +990,9 @@
       <c r="O10">
         <v>85.93994140625</v>
       </c>
+      <c r="V10">
+        <v>91.34999999999999</v>
+      </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="1">
@@ -983,6 +1010,9 @@
       <c r="E11">
         <v>42.14990234375</v>
       </c>
+      <c r="V11">
+        <v>81.78</v>
+      </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1">
@@ -1024,6 +1054,9 @@
       <c r="M12">
         <v>70.9599609375</v>
       </c>
+      <c r="V12">
+        <v>86.83</v>
+      </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="1">
@@ -1035,6 +1068,9 @@
       <c r="C13">
         <v>0</v>
       </c>
+      <c r="V13">
+        <v>48.94</v>
+      </c>
     </row>
     <row r="14" spans="1:22">
       <c r="A14" s="1">
@@ -1079,6 +1115,9 @@
       <c r="N14">
         <v>41.570068359375</v>
       </c>
+      <c r="V14">
+        <v>108.44</v>
+      </c>
     </row>
     <row r="15" spans="1:22">
       <c r="A15" s="1">
@@ -1102,6 +1141,9 @@
       <c r="G15">
         <v>41.169921875</v>
       </c>
+      <c r="V15">
+        <v>74.55</v>
+      </c>
     </row>
     <row r="16" spans="1:22">
       <c r="A16" s="1">
@@ -1131,8 +1173,11 @@
       <c r="I16">
         <v>48.469970703125</v>
       </c>
-    </row>
-    <row r="17" spans="1:18">
+      <c r="V16">
+        <v>74.7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22">
       <c r="A17" s="1">
         <v>19209079</v>
       </c>
@@ -1187,8 +1232,11 @@
       <c r="R17">
         <v>50.97998046875</v>
       </c>
-    </row>
-    <row r="18" spans="1:18">
+      <c r="V17">
+        <v>57.83</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22">
       <c r="A18" s="1">
         <v>19833277</v>
       </c>
@@ -1225,8 +1273,11 @@
       <c r="L18">
         <v>30.3699951171875</v>
       </c>
-    </row>
-    <row r="19" spans="1:18">
+      <c r="V18">
+        <v>74.75</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22">
       <c r="A19" s="1">
         <v>20651178</v>
       </c>
@@ -1245,8 +1296,11 @@
       <c r="F19">
         <v>42.56005859375</v>
       </c>
-    </row>
-    <row r="20" spans="1:18">
+      <c r="V19">
+        <v>63.6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22">
       <c r="A20" s="1">
         <v>44810918</v>
       </c>
@@ -1295,8 +1349,11 @@
       <c r="P20">
         <v>49.280029296875</v>
       </c>
-    </row>
-    <row r="21" spans="1:18">
+      <c r="V20">
+        <v>68.58</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22">
       <c r="A21" s="1">
         <v>47775950</v>
       </c>
@@ -1326,6 +1383,9 @@
       </c>
       <c r="J21">
         <v>42.89990234375</v>
+      </c>
+      <c r="V21">
+        <v>69.15000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao_20.xlsx
+++ b/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao_20.xlsx
@@ -76,7 +76,7 @@
     <t>Rodada 19</t>
   </si>
   <si>
-    <t>Parcial Rodada 16</t>
+    <t>Parcial Rodada 17</t>
   </si>
   <si>
     <t>time_id</t>
@@ -621,10 +621,10 @@
         <v>49.6201171875</v>
       </c>
       <c r="R2">
-        <v>49.6201171875</v>
-      </c>
-      <c r="V2">
-        <v>76.28</v>
+        <v>76.27978515625</v>
+      </c>
+      <c r="S2">
+        <v>76.27978515625</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -680,10 +680,10 @@
         <v>53.929931640625</v>
       </c>
       <c r="R3">
-        <v>53.929931640625</v>
-      </c>
-      <c r="V3">
-        <v>79.2</v>
+        <v>79.2001953125</v>
+      </c>
+      <c r="S3">
+        <v>79.2001953125</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -711,9 +711,6 @@
       <c r="H4">
         <v>47.389892578125</v>
       </c>
-      <c r="V4">
-        <v>72.28</v>
-      </c>
     </row>
     <row r="5" spans="1:22">
       <c r="A5" s="1">
@@ -728,9 +725,6 @@
       <c r="D5">
         <v>44.679931640625</v>
       </c>
-      <c r="V5">
-        <v>96.79000000000001</v>
-      </c>
     </row>
     <row r="6" spans="1:22">
       <c r="A6" s="1">
@@ -785,10 +779,10 @@
         <v>63.75</v>
       </c>
       <c r="R6">
-        <v>63.75</v>
-      </c>
-      <c r="V6">
-        <v>73.08</v>
+        <v>73.080078125</v>
+      </c>
+      <c r="S6">
+        <v>73.080078125</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -825,9 +819,6 @@
       <c r="K7">
         <v>39.699951171875</v>
       </c>
-      <c r="V7">
-        <v>19.51</v>
-      </c>
     </row>
     <row r="8" spans="1:22">
       <c r="A8" s="1">
@@ -881,9 +872,6 @@
       <c r="Q8">
         <v>45.14990234375</v>
       </c>
-      <c r="V8">
-        <v>105.5</v>
-      </c>
     </row>
     <row r="9" spans="1:22">
       <c r="A9" s="1">
@@ -938,10 +926,10 @@
         <v>55.89990234375</v>
       </c>
       <c r="R9">
-        <v>55.89990234375</v>
-      </c>
-      <c r="V9">
-        <v>103.39</v>
+        <v>103.39013671875</v>
+      </c>
+      <c r="S9">
+        <v>103.39013671875</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -990,9 +978,6 @@
       <c r="O10">
         <v>85.93994140625</v>
       </c>
-      <c r="V10">
-        <v>91.34999999999999</v>
-      </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="1">
@@ -1010,9 +995,6 @@
       <c r="E11">
         <v>42.14990234375</v>
       </c>
-      <c r="V11">
-        <v>81.78</v>
-      </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1">
@@ -1054,9 +1036,6 @@
       <c r="M12">
         <v>70.9599609375</v>
       </c>
-      <c r="V12">
-        <v>86.83</v>
-      </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="1">
@@ -1068,9 +1047,6 @@
       <c r="C13">
         <v>0</v>
       </c>
-      <c r="V13">
-        <v>48.94</v>
-      </c>
     </row>
     <row r="14" spans="1:22">
       <c r="A14" s="1">
@@ -1115,9 +1091,6 @@
       <c r="N14">
         <v>41.570068359375</v>
       </c>
-      <c r="V14">
-        <v>108.44</v>
-      </c>
     </row>
     <row r="15" spans="1:22">
       <c r="A15" s="1">
@@ -1141,9 +1114,6 @@
       <c r="G15">
         <v>41.169921875</v>
       </c>
-      <c r="V15">
-        <v>74.55</v>
-      </c>
     </row>
     <row r="16" spans="1:22">
       <c r="A16" s="1">
@@ -1173,11 +1143,8 @@
       <c r="I16">
         <v>48.469970703125</v>
       </c>
-      <c r="V16">
-        <v>74.7</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22">
+    </row>
+    <row r="17" spans="1:19">
       <c r="A17" s="1">
         <v>19209079</v>
       </c>
@@ -1230,13 +1197,13 @@
         <v>50.97998046875</v>
       </c>
       <c r="R17">
-        <v>50.97998046875</v>
-      </c>
-      <c r="V17">
-        <v>57.83</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22">
+        <v>57.830078125</v>
+      </c>
+      <c r="S17">
+        <v>57.830078125</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19">
       <c r="A18" s="1">
         <v>19833277</v>
       </c>
@@ -1273,11 +1240,8 @@
       <c r="L18">
         <v>30.3699951171875</v>
       </c>
-      <c r="V18">
-        <v>74.75</v>
-      </c>
-    </row>
-    <row r="19" spans="1:22">
+    </row>
+    <row r="19" spans="1:19">
       <c r="A19" s="1">
         <v>20651178</v>
       </c>
@@ -1296,11 +1260,8 @@
       <c r="F19">
         <v>42.56005859375</v>
       </c>
-      <c r="V19">
-        <v>63.6</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22">
+    </row>
+    <row r="20" spans="1:19">
       <c r="A20" s="1">
         <v>44810918</v>
       </c>
@@ -1349,11 +1310,8 @@
       <c r="P20">
         <v>49.280029296875</v>
       </c>
-      <c r="V20">
-        <v>68.58</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22">
+    </row>
+    <row r="21" spans="1:19">
       <c r="A21" s="1">
         <v>47775950</v>
       </c>
@@ -1383,9 +1341,6 @@
       </c>
       <c r="J21">
         <v>42.89990234375</v>
-      </c>
-      <c r="V21">
-        <v>69.15000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao_20.xlsx
+++ b/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao_20.xlsx
@@ -76,7 +76,7 @@
     <t>Rodada 19</t>
   </si>
   <si>
-    <t>Parcial Rodada 17</t>
+    <t>Parcial Rodada 18</t>
   </si>
   <si>
     <t>time_id</t>
@@ -624,7 +624,7 @@
         <v>76.27978515625</v>
       </c>
       <c r="S2">
-        <v>76.27978515625</v>
+        <v>58.820068359375</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -683,7 +683,10 @@
         <v>79.2001953125</v>
       </c>
       <c r="S3">
-        <v>79.2001953125</v>
+        <v>66.31982421875</v>
+      </c>
+      <c r="T3">
+        <v>66.31982421875</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -782,7 +785,10 @@
         <v>73.080078125</v>
       </c>
       <c r="S6">
-        <v>73.080078125</v>
+        <v>65.6201171875</v>
+      </c>
+      <c r="T6">
+        <v>65.6201171875</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -929,7 +935,10 @@
         <v>103.39013671875</v>
       </c>
       <c r="S9">
-        <v>103.39013671875</v>
+        <v>60.1201171875</v>
+      </c>
+      <c r="T9">
+        <v>60.1201171875</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -1144,7 +1153,7 @@
         <v>48.469970703125</v>
       </c>
     </row>
-    <row r="17" spans="1:19">
+    <row r="17" spans="1:18">
       <c r="A17" s="1">
         <v>19209079</v>
       </c>
@@ -1199,11 +1208,8 @@
       <c r="R17">
         <v>57.830078125</v>
       </c>
-      <c r="S17">
-        <v>57.830078125</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19">
+    </row>
+    <row r="18" spans="1:18">
       <c r="A18" s="1">
         <v>19833277</v>
       </c>
@@ -1241,7 +1247,7 @@
         <v>30.3699951171875</v>
       </c>
     </row>
-    <row r="19" spans="1:19">
+    <row r="19" spans="1:18">
       <c r="A19" s="1">
         <v>20651178</v>
       </c>
@@ -1261,7 +1267,7 @@
         <v>42.56005859375</v>
       </c>
     </row>
-    <row r="20" spans="1:19">
+    <row r="20" spans="1:18">
       <c r="A20" s="1">
         <v>44810918</v>
       </c>
@@ -1311,7 +1317,7 @@
         <v>49.280029296875</v>
       </c>
     </row>
-    <row r="21" spans="1:19">
+    <row r="21" spans="1:18">
       <c r="A21" s="1">
         <v>47775950</v>
       </c>

--- a/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao_20.xlsx
+++ b/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao_20.xlsx
@@ -76,7 +76,7 @@
     <t>Rodada 19</t>
   </si>
   <si>
-    <t>Parcial Rodada 18</t>
+    <t>Parcial Rodada 19</t>
   </si>
   <si>
     <t>time_id</t>
@@ -686,7 +686,7 @@
         <v>66.31982421875</v>
       </c>
       <c r="T3">
-        <v>66.31982421875</v>
+        <v>110.0498046875</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -788,7 +788,10 @@
         <v>65.6201171875</v>
       </c>
       <c r="T6">
-        <v>65.6201171875</v>
+        <v>111.64990234375</v>
+      </c>
+      <c r="U6">
+        <v>111.64990234375</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -938,7 +941,10 @@
         <v>60.1201171875</v>
       </c>
       <c r="T9">
-        <v>60.1201171875</v>
+        <v>132.9501953125</v>
+      </c>
+      <c r="U9">
+        <v>132.9501953125</v>
       </c>
     </row>
     <row r="10" spans="1:22">
